--- a/uploads/reports/monthly_report_2026-02.xlsx
+++ b/uploads/reports/monthly_report_2026-02.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="184">
   <si>
     <t>AttemptId</t>
   </si>
@@ -47,22 +47,132 @@
     <t>AiFeedback</t>
   </si>
   <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>hoanganhnd2003@gmail.com</t>
+  </si>
+  <si>
+    <t>Hoàng Anh Nguyễn</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>PRACTICE</t>
+  </si>
+  <si>
+    <t>2026-02-04T16:51:08.886226</t>
+  </si>
+  <si>
+    <t>2026-02-04T16:52:06.301896</t>
+  </si>
+  <si>
+    <t>[{"questionId":829,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sadsa","sampleAnswer":"Tài liệu chỉ ra rằng Next.js có sự phân biệt giữa cơ chế server side và client side. Điều này ngụ ý rằng Next.js có thể xử lý việc render và tương tác ở cả phía máy chủ và phía trình duyệt. Khả năng này cho phép các chiến lược khác nhau trong việc xây dựng ứng dụng web, tận dụng ưu điểm của cả hai môi trường.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":830,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":831,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":832,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sadsd","sampleAnswer":"Tài liệu liệt kê ba chức năng chính của `router dom`. Thứ nhất là \"router basic\", dùng cho định tuyến cơ bản. Thứ hai là \"router lấy tham số trên url\", cho phép trích xuất dữ liệu từ URL. Cuối cùng là \"chuyển hướng\", giúp điều hướng người dùng đến các trang khác trong ứng dụng.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":833,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":834,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":835,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sadsada","sampleAnswer":"Theo tài liệu, Redux bao gồm các thành phần cơ bản và đặc biệt là thư viện Redux Toolkit. Redux Toolkit được giới thiệu như một bộ công cụ giúp đơn giản hóa quá trình phát triển Redux. Nó cung cấp các tiện ích để viết code Redux hiệu quả và dễ dàng hơn, giúp giảm bớt boilerplate code.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":836,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":837,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":838,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Chào Hoàng Anh Nguyễn.
+- Điểm tổng: 60/100
+- Điểm tổng 60/100 cho thấy bạn có nắm được một phần kiến thức cơ bản.
+- Bạn làm khá tốt các câu hỏi trắc nghiệm nhưng còn gặp nhiều khó khăn ở các câu hỏi tự luận.
+- Lỗi sai nổi bật nhất là bạn đã bỏ trống hoặc điền câu trả lời không liên quan cho tất cả các câu hỏi tự luận (Câu 1, 4, 7).
+- Điều này cho thấy bạn chưa nắm vững kiến thức chuyên sâu hoặc kỹ năng trình bày các khái niệm được yêu cầu giải thích.
+- Bạn còn sai một câu hỏi trắc nghiệm về `router dom` (Câu 10).
+- Hãy tập trung ôn luyện lại các khái niệm yêu cầu giải thích chi tiết, đặc biệt là về Next.js (phân biệt server/client side) và các chức năng của `router dom`.</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>2026-02-04T16:48:23.802722</t>
+  </si>
+  <si>
+    <t>2026-02-04T16:49:42.780638</t>
+  </si>
+  <si>
+    <t>[{"questionId":819,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":820,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ádasf","sampleAnswer":"Tài liệu chỉ ra rằng Next.js có sự phân biệt giữa cơ chế server side và client side. Điều này ngụ ý rằng Next.js có thể xử lý việc render và tương tác ở cả phía máy chủ và phía trình duyệt, cho phép các chiến lược khác nhau trong việc xây dựng ứng dụng web.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":821,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":822,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":823,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sad","sampleAnswer":"Theo tài liệu, Redux bao gồm các thành phần cơ bản và đặc biệt là thư viện Redux Toolkit. Redux Toolkit được giới thiệu như một bộ công cụ giúp đơn giản hóa quá trình phát triển Redux, cung cấp các tiện ích để viết code Redux hiệu quả hơn.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":824,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":825,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":826,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ádsad","sampleAnswer":"Tài liệu liệt kê ba chức năng chính của `router dom`. Đó là 'router basic' (định tuyến cơ bản), 'router lấy tham số trên url' (khả năng trích xuất dữ liệu từ URL), và 'chuyển hướng' (khả năng điều hướng người dùng đến các trang khác).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":827,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":828,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Chào Hoàng Anh Nguyễn.
+- Điểm tổng: 60/100
+- Bạn đã đạt được điểm khá ở phần trắc nghiệm, cho thấy bạn có nắm vững một số kiến thức cơ bản trong tài liệu.
+- Tuy nhiên, bạn cần cải thiện đáng kể ở các câu hỏi tự luận và diễn giải.
+- Lỗi sai nổi bật nhất là khả năng trả lời các câu hỏi tự luận, khi tất cả các câu hỏi dạng này đều chưa được trả lời đúng hoặc đầy đủ.
+- Bạn gặp khó khăn trong việc tổng hợp và diễn đạt thông tin từ tài liệu cho các khái niệm như cơ chế server/client side trong Next.js hay các thành phần của Redux.
+- Có một câu hỏi trắc nghiệm về phân biệt cơ chế trong Next.js bạn chọn sai, cho thấy cần xem xét kỹ hơn về chủ đề này.
+- Hãy dành thời gian đọc kỹ và sâu hơn các tài liệu, đặc biệt là các phần giải thích khái niệm và cơ chế.</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>2026-02-04T14:36:12.424293</t>
+  </si>
+  <si>
+    <t>2026-02-04T14:36:54.229126</t>
+  </si>
+  <si>
+    <t>[{"questionId":809,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":810,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sadasd","sampleAnswer":"IoC Container là thành phần lõi của Spring, chịu trách nhiệm tạo bean, inject dependency và quản lý vòng đời bean. Nó đảm bảo các object được khởi tạo và liên kết đúng cách. Hai loại IoC Container phổ biến là BeanFactory (cơ bản, nhẹ) và ApplicationContext (nâng cao, dùng phổ biến, mặc định trong Spring Boot).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":811,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":812,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":813,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dfasf","sampleAnswer":"Client gửi request cho DispatcherServlet. DispatcherServlet sử dụng HandlerMapping để ánh xạ tới Controller phù hợp. Controller gọi các phương thức xử lý, thiết lập Model dữ liệu và trả về tên View. DispatcherServlet dùng ViewResolver để xác định View, sau đó chuyển Model cho View để render và trả HTTP response về cho Client.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":814,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":815,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":816,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sấd","sampleAnswer":"IoC là nguyên lý thiết kế trong đó Spring Framework chịu trách nhiệm tạo, quản lý, liên kết và huỷ object thay cho lập trình viên. Mục đích chính là đảo ngược quyền kiểm soát việc tạo dependency cho Spring. Các lợi ích bao gồm tránh phụ thuộc chặt giữa các class, dễ thay đổi implementation, dễ test (mock), và giúp code linh hoạt, dễ bảo trì.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":817,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":818,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Chào Hoàng Anh Nguyễn.
+- Điểm tổng 60/100 cho thấy bạn có nắm vững một số kiến thức cơ bản về Spring Framework.
+- Bạn làm tốt ở các câu hỏi trắc nghiệm về định nghĩa, annotation và vai trò của các thành phần riêng lẻ.
+- Tuy nhiên, bạn cần cải thiện đáng kể ở các câu hỏi tự luận và các nguyên lý cốt lõi của Spring.
+- Lỗi sai nổi bật:
+- Bạn chưa nắm vững nguyên lý Inversion of Control (IoC), mục đích và lợi ích của nó.
+- Kiến thức về vai trò chính và các loại IoC Container còn hạn chế.
+- Bạn gặp khó khăn trong việc mô tả luồng xử lý HTTP request trong Spring MVC.</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>hoanganhyb2003@gmail.com</t>
+  </si>
+  <si>
+    <t>Hoang Anh Nguyen</t>
+  </si>
+  <si>
+    <t>2026-02-04T14:19:22.551509</t>
+  </si>
+  <si>
+    <t>2026-02-04T14:24:42.867705</t>
+  </si>
+  <si>
+    <t>[{"questionId":799,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":800,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"server-side tạo HTML trên máy chủ, tối ưu SEO tốc độ tải đầu\nclient-side render bằng JavaScript bằng trình duyệt","sampleAnswer":"Trong Next.js, cơ chế server-side liên quan đến việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động.","score":8,"maxScore":10,"feedback":"Thiếu ý: Next.js"},{"questionId":801,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":802,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":803,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Redux là thư viện quản lý trạng \ncác thành phần chính là \nstore, action, reducer, reduxtoolkit","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Các thành phần chính của Redux bao gồm store (nơi lưu trữ trạng thái), actions (các đối tượng mô tả sự kiện đã xảy ra), và reducers (các hàm thuần túy xác định cách trạng thái thay đổi để phản ứng với actions). Ngoài ra, tài liệu còn nhắc đến thư viện Redux Toolkit giúp đơn giản hóa việc sử dụng Redux.","score":4,"maxScore":10,"feedback":"Thiếu ý: actions, reducers, Redux Toolkit"},{"questionId":804,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":805,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":806,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"không biết","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm định tuyến cơ bản (router basic), khả năng lấy tham số từ URL (router lấy tham số trên url), và chức năng chuyển hướng (chuyển hướng).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":807,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":808,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoang Anh Nguyen,
+- Chào Hoang Anh Nguyen.
+- Điểm tổng: 82/100
+- Bạn có kết quả bài làm tốt với 82/100 điểm, cho thấy sự nắm vững kiến thức nền tảng.
+- Các câu hỏi trắc nghiệm đều được trả lời đúng, thể hiện khả năng ghi nhớ và nhận diện thông tin tốt.
+- Bạn cần chú ý cải thiện ở các câu hỏi tự luận để đạt điểm tối đa.
+- Phần giải thích về Redux (câu 5) chỉ liệt kê các thành phần mà chưa đi vào giải thích chi tiết vai trò của từng mục.
+- Bạn chưa nắm được hoặc bỏ trống câu hỏi về các chức năng cơ bản của router (câu 8).
+- Câu trả lời về server-side và client-side trong Next.js (câu 2) còn khá ngắn gọn, có thể bổ sung thêm chi tiết.</t>
+  </si>
+  <si>
     <t>83</t>
   </si>
   <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>hoanganhnd2003@gmail.com</t>
-  </si>
-  <si>
-    <t>Hoàng Anh Nguyễn</t>
-  </si>
-  <si>
     <t>90</t>
-  </si>
-  <si>
-    <t>PRACTICE</t>
   </si>
   <si>
     <t>2026-02-03T14:07:05.349100</t>
@@ -140,9 +250,6 @@
     <t>80</t>
   </si>
   <si>
-    <t>87</t>
-  </si>
-  <si>
     <t>2026-02-03T12:17:09.142761</t>
   </si>
   <si>
@@ -166,9 +273,6 @@
     <t>79</t>
   </si>
   <si>
-    <t>86</t>
-  </si>
-  <si>
     <t>2026-02-03T11:20:45.167648</t>
   </si>
   <si>
@@ -192,9 +296,6 @@
     <t>78</t>
   </si>
   <si>
-    <t>85</t>
-  </si>
-  <si>
     <t>2026-02-03T10:52:21.445947</t>
   </si>
   <si>
@@ -216,9 +317,6 @@
   </si>
   <si>
     <t>77</t>
-  </si>
-  <si>
-    <t>84</t>
   </si>
   <si>
     <t>2026-02-03T10:50:38.476897</t>
@@ -426,15 +524,6 @@
   </si>
   <si>
     <t>68</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>hoanganhyb2003@gmail.com</t>
-  </si>
-  <si>
-    <t>Hoang Anh Nguyen</t>
   </si>
   <si>
     <t>2026-02-02T14:04:37.691325</t>
@@ -770,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.18359375" customWidth="true" bestFit="true"/>
@@ -847,7 +936,7 @@
         <v>18</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="J2" t="s" s="0">
         <v>19</v>
@@ -882,7 +971,7 @@
         <v>24</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>24.0</v>
+        <v>60.0</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>25</v>
@@ -917,7 +1006,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>70.0</v>
+        <v>60.0</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>31</v>
@@ -931,39 +1020,39 @@
         <v>33</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>70.0</v>
+        <v>82.0</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>12</v>
@@ -975,30 +1064,30 @@
         <v>14</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>70.0</v>
+        <v>40.0</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>12</v>
@@ -1010,30 +1099,30 @@
         <v>14</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>40.0</v>
+        <v>24.0</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>12</v>
@@ -1045,30 +1134,30 @@
         <v>14</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I8" t="n" s="0">
         <v>70.0</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>12</v>
@@ -1086,24 +1175,24 @@
         <v>16</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I9" t="n" s="0">
         <v>70.0</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>12</v>
@@ -1121,24 +1210,24 @@
         <v>16</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I10" t="n" s="0">
         <v>70.0</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>12</v>
@@ -1156,24 +1245,24 @@
         <v>16</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>12</v>
@@ -1191,24 +1280,24 @@
         <v>16</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>12</v>
@@ -1220,30 +1309,30 @@
         <v>14</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>30.0</v>
+        <v>70.0</v>
       </c>
       <c r="J13" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>12</v>
@@ -1255,30 +1344,30 @@
         <v>14</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>20.0</v>
+        <v>70.0</v>
       </c>
       <c r="J14" t="s" s="0">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>12</v>
@@ -1290,30 +1379,30 @@
         <v>14</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I15" t="n" s="0">
         <v>20.0</v>
       </c>
       <c r="J15" t="s" s="0">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>12</v>
@@ -1325,480 +1414,620 @@
         <v>14</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>30.0</v>
+        <v>60.0</v>
       </c>
       <c r="J16" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G17" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="E17" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G17" t="s" s="0">
+      <c r="H17" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="H17" t="s" s="0">
+      <c r="I17" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="J17" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="I17" t="n" s="0">
-        <v>60.0</v>
-      </c>
-      <c r="J17" t="s" s="0">
+      <c r="K17" t="s" s="0">
         <v>103</v>
-      </c>
-      <c r="K17" t="s" s="0">
-        <v>104</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G18" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="B18" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>67</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G18" t="s" s="0">
+      <c r="H18" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="H18" t="s" s="0">
+      <c r="I18" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="J18" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="I18" t="n" s="0">
-        <v>50.0</v>
-      </c>
-      <c r="J18" t="s" s="0">
+      <c r="K18" t="s" s="0">
         <v>108</v>
-      </c>
-      <c r="K18" t="s" s="0">
-        <v>109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G19" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="B19" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="F19" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G19" t="s" s="0">
+      <c r="H19" t="s" s="0">
         <v>111</v>
       </c>
-      <c r="H19" t="s" s="0">
+      <c r="I19" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="J19" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="I19" t="n" s="0">
-        <v>81.0</v>
-      </c>
-      <c r="J19" t="s" s="0">
+      <c r="K19" t="s" s="0">
         <v>113</v>
-      </c>
-      <c r="K19" t="s" s="0">
-        <v>114</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G20" t="s" s="0">
         <v>115</v>
       </c>
-      <c r="B20" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E20" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="F20" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G20" t="s" s="0">
+      <c r="H20" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="H20" t="s" s="0">
+      <c r="I20" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="J20" t="s" s="0">
         <v>117</v>
       </c>
-      <c r="I20" t="n" s="0">
-        <v>60.0</v>
-      </c>
-      <c r="J20" t="s" s="0">
+      <c r="K20" t="s" s="0">
         <v>118</v>
-      </c>
-      <c r="K20" t="s" s="0">
-        <v>119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G21" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="B21" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="D21" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="E21" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="F21" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G21" t="s" s="0">
+      <c r="H21" t="s" s="0">
         <v>121</v>
       </c>
-      <c r="H21" t="s" s="0">
+      <c r="I21" t="n" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="J21" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="I21" t="n" s="0">
-        <v>77.0</v>
-      </c>
-      <c r="J21" t="s" s="0">
+      <c r="K21" t="s" s="0">
         <v>123</v>
-      </c>
-      <c r="K21" t="s" s="0">
-        <v>124</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G22" t="s" s="0">
         <v>125</v>
       </c>
-      <c r="B22" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D22" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="F22" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G22" t="s" s="0">
+      <c r="H22" t="s" s="0">
         <v>126</v>
-      </c>
-      <c r="H22" t="s" s="0">
-        <v>127</v>
       </c>
       <c r="I22" t="n" s="0">
         <v>50.0</v>
       </c>
       <c r="J22" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="K22" t="s" s="0">
         <v>128</v>
-      </c>
-      <c r="K22" t="s" s="0">
-        <v>129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G23" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="B23" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D23" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="F23" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G23" t="s" s="0">
+      <c r="H23" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="H23" t="s" s="0">
+      <c r="I23" t="n" s="0">
+        <v>81.0</v>
+      </c>
+      <c r="J23" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="I23" t="n" s="0">
-        <v>60.0</v>
-      </c>
-      <c r="J23" t="s" s="0">
+      <c r="K23" t="s" s="0">
         <v>133</v>
-      </c>
-      <c r="K23" t="s" s="0">
-        <v>134</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G24" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="B24" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C24" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D24" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="F24" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G24" t="s" s="0">
+      <c r="H24" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="H24" t="s" s="0">
+      <c r="I24" t="n" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="J24" t="s" s="0">
         <v>137</v>
       </c>
-      <c r="I24" t="n" s="0">
-        <v>30.0</v>
-      </c>
-      <c r="J24" t="s" s="0">
+      <c r="K24" t="s" s="0">
         <v>138</v>
-      </c>
-      <c r="K24" t="s" s="0">
-        <v>139</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G25" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="B25" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D25" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E25" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="F25" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G25" t="s" s="0">
+      <c r="H25" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="H25" t="s" s="0">
+      <c r="I25" t="n" s="0">
+        <v>77.0</v>
+      </c>
+      <c r="J25" t="s" s="0">
         <v>142</v>
       </c>
-      <c r="I25" t="n" s="0">
-        <v>70.0</v>
-      </c>
-      <c r="J25" t="s" s="0">
+      <c r="K25" t="s" s="0">
         <v>143</v>
-      </c>
-      <c r="K25" t="s" s="0">
-        <v>144</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G26" t="s" s="0">
         <v>145</v>
       </c>
-      <c r="B26" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C26" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D26" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s" s="0">
-        <v>110</v>
-      </c>
-      <c r="F26" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G26" t="s" s="0">
+      <c r="H26" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="H26" t="s" s="0">
+      <c r="I26" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="J26" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="I26" t="n" s="0">
-        <v>87.0</v>
-      </c>
-      <c r="J26" t="s" s="0">
+      <c r="K26" t="s" s="0">
         <v>148</v>
-      </c>
-      <c r="K26" t="s" s="0">
-        <v>149</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G27" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="B27" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C27" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D27" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E27" t="s" s="0">
-        <v>115</v>
-      </c>
-      <c r="F27" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G27" t="s" s="0">
+      <c r="H27" t="s" s="0">
         <v>151</v>
       </c>
-      <c r="H27" t="s" s="0">
+      <c r="I27" t="n" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="J27" t="s" s="0">
         <v>152</v>
       </c>
-      <c r="I27" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="J27" t="s" s="0">
+      <c r="K27" t="s" s="0">
         <v>153</v>
-      </c>
-      <c r="K27" t="s" s="0">
-        <v>154</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G28" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="B28" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C28" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D28" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E28" t="s" s="0">
-        <v>120</v>
-      </c>
-      <c r="F28" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G28" t="s" s="0">
+      <c r="H28" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="H28" t="s" s="0">
+      <c r="I28" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="J28" t="s" s="0">
         <v>157</v>
       </c>
-      <c r="I28" t="n" s="0">
-        <v>40.0</v>
-      </c>
-      <c r="J28" t="s" s="0">
+      <c r="K28" t="s" s="0">
         <v>158</v>
-      </c>
-      <c r="K28" t="s" s="0">
-        <v>159</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G29" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="B29" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C29" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s" s="0">
-        <v>125</v>
-      </c>
-      <c r="F29" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G29" t="s" s="0">
+      <c r="H29" t="s" s="0">
         <v>161</v>
       </c>
-      <c r="H29" t="s" s="0">
+      <c r="I29" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J29" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="I29" t="n" s="0">
+      <c r="K29" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="I30" t="n" s="0">
+        <v>87.0</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="K30" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="I31" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="K31" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="I32" t="n" s="0">
         <v>40.0</v>
       </c>
-      <c r="J29" t="s" s="0">
-        <v>163</v>
-      </c>
-      <c r="K29" t="s" s="0">
-        <v>164</v>
+      <c r="J32" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="K32" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="I33" t="n" s="0">
+        <v>40.0</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="K33" t="s" s="0">
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/reports/monthly_report_2026-02.xlsx
+++ b/uploads/reports/monthly_report_2026-02.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="329">
   <si>
     <t>AttemptId</t>
   </si>
@@ -47,22 +47,708 @@
     <t>AiFeedback</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>hoanganhnd2003@gmail.com</t>
+  </si>
+  <si>
+    <t>Hoàng Anh Nguyễn</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>PRACTICE</t>
+  </si>
+  <si>
+    <t>2026-02-08T22:35:48.666195</t>
+  </si>
+  <si>
+    <t>2026-02-08T22:36:09.576869</t>
+  </si>
+  <si>
+    <t>[{"questionId":1119,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1120,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"f","sampleAnswer":"Trong Next.js, cơ chế server-side liên quan đến việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1121,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1122,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1123,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"f","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Các thành phần chính của Redux bao gồm store (nơi lưu trữ trạng thái), actions (các đối tượng mô tả sự kiện đã xảy ra), và reducers (các hàm thuần túy xác định cách trạng thái thay đổi để phản ứng với actions). Ngoài ra, tài liệu còn nhắc đến thư viện Redux Toolkit giúp đơn giản hóa việc sử dụng Redux.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1124,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1125,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1126,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"f","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm định tuyến cơ bản (router basic), khả năng lấy tham số từ URL (router lấy tham số trên url), và chức năng chuyển hướng (chuyển hướng).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1127,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1128,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+Điểm mạnh:
+- Học viên nắm vững kiến thức cơ bản và khả năng nhận diện đáp án đúng cho các câu hỏi trắc nghiệm.
+- Đã trả lời chính xác tất cả các câu hỏi trắc nghiệm liên quan đến React (memo, ref, context, form bằng state), thư viện API client và Redux Toolkit.
+Điểm yếu:
+- Học viên chưa thể hiện được khả năng giải thích và phân biệt rõ ràng các khái niệm chuyên sâu.
+- Các câu hỏi yêu cầu giải thích hoặc liệt kê chi tiết (cơ chế server-side/client-side Next.js, định nghĩa và thành phần Redux, chức năng router) đều chưa được trả lời đúng.
+Gợi ý ôn tập:
+- Tập trung ôn lại các khái niệm cần giải thích rõ ràng như cơ chế render trong Next.js, Redux và các thành phần cốt lõi, cũng như các chức năng của router theo tài liệu.
+- Thực hành diễn giải lại các kiến thức đã học bằng lời văn của mình, không chỉ dừng lại ở việc nhận diện đáp án đúng.
+- Đọc kỹ và ghi chú các phần giải thích trong tài liệu để có thể trình bày lại một cách đầy đủ và chính xác.</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>2026-02-08T22:27:53.682190</t>
+  </si>
+  <si>
+    <t>2026-02-08T22:28:16.569591</t>
+  </si>
+  <si>
+    <t>[{"questionId":1109,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":1110,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"q","sampleAnswer":"IoC Container là thành phần lõi của Spring, chịu trách nhiệm tạo bean, inject dependency và quản lý vòng đời bean. Nó đảm bảo các object được khởi tạo và liên kết đúng cách. Hai loại IoC Container phổ biến là BeanFactory (cơ bản, nhẹ) và ApplicationContext (nâng cao, dùng phổ biến, mặc định trong Spring Boot).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1111,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1112,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1113,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"qư","sampleAnswer":"Client gửi request cho DispatcherServlet. DispatcherServlet sử dụng HandlerMapping để ánh xạ tới Controller phù hợp. Controller gọi các phương thức xử lý, thiết lập Model dữ liệu và trả về tên View. DispatcherServlet dùng ViewResolver để xác định View, sau đó chuyển Model cho View để render và trả HTTP response về cho Client.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1114,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1115,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1116,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"qư","sampleAnswer":"IoC là nguyên lý thiết kế trong đó Spring Framework chịu trách nhiệm tạo, quản lý, liên kết và huỷ object thay cho lập trình viên. Mục đích chính là đảo ngược quyền kiểm soát việc tạo dependency cho Spring. Các lợi ích bao gồm tránh phụ thuộc chặt giữa các class, dễ thay đổi implementation, dễ test (mock), và giúp code linh hoạt, dễ bảo trì.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1117,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1118,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+Điểm mạnh:
+- Nắm vững các câu hỏi trắc nghiệm liên quan đến định nghĩa API và annotation cụ thể.
+- Trả lời chính xác về phạm vi tồn tại mặc định của Spring Bean và vai trò của DispatcherServlet.
+- Hiểu đúng về sự khác biệt giữa @PathVariable và @RequestParam, cũng như giữa HTTP GET và HTTP POST.
+Điểm yếu:
+- Chưa nắm vững các nguyên lý cốt lõi của Spring Framework như Inversion of Control (IoC) và Dependency Injection (DI).
+- Khả năng mô tả và giải thích các khái niệm quan trọng như trách nhiệm của IoC Container hoặc luồng xử lý Spring MVC còn hạn chế.
+- Các câu hỏi yêu cầu giải thích hoặc định nghĩa sâu về Spring Framework thường chưa được trả lời đầy đủ hoặc chính xác.
+Gợi ý ôn tập:
+- Tập trung ôn lại các nguyên lý thiết kế chính của Spring như IoC và DI, bao gồm cả mục đích, lợi ích và cách thức hoạt động.
+- Nắm vững vai trò và các thành phần của IoC Container, cùng với các loại Container phổ biến.
+- Thực hành mô tả chi tiết luồng xử lý của một request trong Spring MVC để hiểu rõ sự tương tác giữa các component.</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>2026-02-08T22:18:04.226823</t>
+  </si>
+  <si>
+    <t>2026-02-08T22:18:20.653830</t>
+  </si>
+  <si>
+    <t>[{"questionId":1099,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1100,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"f","sampleAnswer":"Trong Next.js, cơ chế server-side liên quan đến việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1101,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1102,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1103,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"f","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Các thành phần chính của Redux bao gồm store (nơi lưu trữ trạng thái), actions (các đối tượng mô tả sự kiện đã xảy ra), và reducers (các hàm thuần túy xác định cách trạng thái thay đổi để phản ứng với actions). Ngoài ra, tài liệu còn nhắc đến thư viện Redux Toolkit giúp đơn giản hóa việc sử dụng Redux.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1104,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1105,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1106,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"f","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm định tuyến cơ bản (router basic), khả năng lấy tham số từ URL (router lấy tham số trên url), và chức năng chuyển hướng (chuyển hướng).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1107,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1108,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+Điểm mạnh:
+- Bạn đã hoàn thành bài và có nỗ lực trả lời.
+- Một số ý trả lời đúng hướng theo học liệu.
+Điểm yếu:
+- Còn thiếu/nhầm ở các ý trọng tâm trong một số câu.
+- Trình bày chưa đủ rõ, thiếu keywords quan trọng.
+Gợi ý ôn tập:
+- Xem lại các câu sai trong phần “Xem lại đáp án”.
+- Ôn lại khái niệm chính và ví dụ trong học liệu.
+- Làm lại bài dưới giới hạn thời gian để tăng tốc độ.</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>2026-02-08T21:54:38.109409</t>
+  </si>
+  <si>
+    <t>2026-02-08T21:54:58.326367</t>
+  </si>
+  <si>
+    <t>[{"questionId":1089,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1090,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ề","sampleAnswer":"Để xử lý form bằng state trong React, chúng ta sử dụng các 'controlled components'. Mỗi input trong form sẽ có giá trị được kiểm soát bởi state của component. Khi người dùng nhập liệu, sự kiện `onChange` sẽ được kích hoạt để cập nhật state, từ đó cập nhật lại giá trị của input. Điều này giúp quản lý và truy cập dữ liệu form một cách dễ dàng và nhất quán.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1091,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":1092,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1093,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ád","sampleAnswer":"`router dom` cung cấp các thành phần để xây dựng định tuyến client-side. Các khái niệm cơ bản bao gồm `BrowserRouter` để bao bọc ứng dụng và cung cấp ngữ cảnh định tuyến. `Routes` được dùng để định nghĩa tập hợp các tuyến đường, và `Route` để ánh xạ một URL cụ thể với một component sẽ được render. `Link` được sử dụng để điều hướng giữa các trang mà không cần tải lại toàn bộ trang.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1094,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1095,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1096,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sad","sampleAnswer":"Trong Next.js, cơ chế server-side (như SSR hoặc SSG) là khi trang được render trước trên server và gửi HTML đã hoàn chỉnh đến trình duyệt. Điều này giúp cải thiện SEO và thời gian tải ban đầu. Cơ chế client-side là khi trang được render hoặc tương tác sau khi JavaScript đã được tải xuống và thực thi trên trình duyệt, thường là sau quá trình 'hydration' của Next.js, cho phép các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1097,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1098,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+Điểm mạnh:
+- Nắm vững một số khái niệm cơ bản trong React như `memo`, `ref`, `context`.
+- Có kiến thức tốt về các thư viện API client phổ biến và một ưu điểm của Next.js.
+Điểm yếu:
+- Kiến thức về `router dom` còn yếu, đặc biệt là cách lấy tham số từ URL và thực hiện chuyển hướng lập trình.
+- Kỹ năng trả lời câu hỏi tự luận chưa tốt, các câu trả lời quá ngắn gọn và không đúng trọng tâm.
+- Chưa hiểu rõ hoặc chưa thể diễn giải được cách xử lý form bằng state trong React, các khái niệm cơ bản về router trong `router dom` và phân biệt cơ chế server-side/client-side trong Next.js.
+Gợi ý ôn tập:
+- Tập trung ôn lại toàn bộ kiến thức về `router dom`, đặc biệt là các hook để lấy tham số URL và điều hướng lập trình.
+- Dành thời gian luyện tập trả lời các câu hỏi tự luận, cố gắng diễn giải các khái niệm một cách đầy đủ và rõ ràng.
+- Xem lại chi tiết cách xử lý form với controlled components trong React, hiểu rõ vai trò của state và sự kiện `onChange`.
+- Nghiên cứu sâu hơn về các khái niệm cơ bản của `router dom` như `BrowserRouter`, `Routes`, `Route`, `Link` và sự khác biệt giữa server-side rendering, client-side rendering trong Next.js.</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>2026-02-08T21:43:24.435074</t>
+  </si>
+  <si>
+    <t>2026-02-08T21:43:41.175294</t>
+  </si>
+  <si>
+    <t>[{"questionId":1079,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1080,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dfs","sampleAnswer":"Để xử lý form bằng state trong React, chúng ta sử dụng các 'controlled components'. Mỗi input trong form sẽ có giá trị được kiểm soát bởi state của component. Khi người dùng nhập liệu, sự kiện `onChange` sẽ được kích hoạt để cập nhật state, từ đó cập nhật lại giá trị của input. Điều này giúp quản lý và truy cập dữ liệu form một cách dễ dàng và nhất quán.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1081,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1082,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1083,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sad","sampleAnswer":"`router dom` cung cấp các thành phần để xây dựng định tuyến client-side. Các khái niệm cơ bản bao gồm `BrowserRouter` để bao bọc ứng dụng và cung cấp ngữ cảnh định tuyến. `Routes` được dùng để định nghĩa tập hợp các tuyến đường, và `Route` để ánh xạ một URL cụ thể với một component sẽ được render. `Link` được sử dụng để điều hướng giữa các trang mà không cần tải lại toàn bộ trang.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1084,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1085,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1086,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sad","sampleAnswer":"Trong Next.js, cơ chế server-side (như SSR hoặc SSG) là khi trang được render trước trên server và gửi HTML đã hoàn chỉnh đến trình duyệt. Điều này giúp cải thiện SEO và thời gian tải ban đầu. Cơ chế client-side là khi trang được render hoặc tương tác sau khi JavaScript đã được tải xuống và thực thi trên trình duyệt, thường là sau quá trình 'hydration' của Next.js, cho phép các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1087,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1088,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+Điểm mạnh:
+- Học viên trả lời đúng và đầy đủ các câu hỏi trắc nghiệm, cho thấy nắm vững kiến thức cơ bản về React và React Router DOM.
+- Có sự hiểu biết tốt về các hook và cơ chế quan trọng như `memo`, `ref`, `context`, `useNavigate`.
+Điểm yếu:
+- Các câu hỏi tự luận chưa được trả lời hoặc trả lời không đúng, cho thấy kiến thức chưa sâu ở mảng giải thích và mô tả.
+- Kỹ năng diễn đạt và trình bày các khái niệm chi tiết còn hạn chế.
+Gợi ý ôn tập:
+- Tập trung ôn luyện sâu hơn các khái niệm yêu cầu giải thích, đặc biệt là cách xử lý form bằng state trong React, các thành phần cơ bản của React Router DOM và cơ chế render trong Next.js.
+- Thực hành viết mô tả và giải thích ngắn gọn, súc tích cho các khái niệm đã học.
+- Tìm hiểu kỹ các từ khóa trong phần đáp án mẫu để mở rộng kiến thức và có thể trả lời các câu hỏi tự luận một cách chi tiết hơn.</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>2026-02-08T21:19:17.339590</t>
+  </si>
+  <si>
+    <t>2026-02-08T21:21:35.553218</t>
+  </si>
+  <si>
+    <t>[{"questionId":1069,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1070,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ádsa","sampleAnswer":"Để xử lý form bằng state trong React, chúng ta sử dụng các 'controlled components'. Mỗi input trong form sẽ có giá trị được kiểm soát bởi state của component. Khi người dùng nhập liệu, sự kiện `onChange` sẽ được kích hoạt để cập nhật state, từ đó cập nhật lại giá trị của input. Điều này giúp quản lý và truy cập dữ liệu form một cách dễ dàng và nhất quán.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1071,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1072,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1073,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ds","sampleAnswer":"`router dom` cung cấp các thành phần để xây dựng định tuyến client-side. Các khái niệm cơ bản bao gồm `BrowserRouter` để bao bọc ứng dụng và cung cấp ngữ cảnh định tuyến. `Routes` được dùng để định nghĩa tập hợp các tuyến đường, và `Route` để ánh xạ một URL cụ thể với một component sẽ được render. `Link` được sử dụng để điều hướng giữa các trang mà không cần tải lại toàn bộ trang.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1074,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1075,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1076,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sad","sampleAnswer":"Trong Next.js, cơ chế server-side (như SSR hoặc SSG) là khi trang được render trước trên server và gửi HTML đã hoàn chỉnh đến trình duyệt. Điều này giúp cải thiện SEO và thời gian tải ban đầu. Cơ chế client-side là khi trang được render hoặc tương tác sau khi JavaScript đã được tải xuống và thực thi trên trình duyệt, thường là sau quá trình 'hydration' của Next.js, cho phép các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1077,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1078,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+Điểm mạnh:
+- Bạn đã trả lời đúng tất cả các câu hỏi trắc nghiệm, cho thấy sự nắm vững các khái niệm cơ bản về React (memo, ref, context) và cách sử dụng React Router DOM (lấy tham số URL, chuyển hướng lập trình).
+- Bạn cũng đã nhận diện chính xác ưu điểm của Next.js và các thư viện API client phổ biến.
+Điểm yếu:
+- Các câu trả lời cho câu hỏi tự luận còn trống hoặc chỉ là văn bản không liên quan, cho thấy bạn chưa nắm vững cách diễn giải hoặc mô tả các khái niệm chi tiết.
+- Bạn chưa thể giải thích được cơ chế xử lý form bằng state, các khái niệm cơ bản về router trong React Router DOM, và sự khác biệt giữa server-side và client-side trong Next.js.
+Gợi ý ôn tập:
+- Tập trung ôn lại các kiến thức lý thuyết và cách mô tả chi tiết các khái niệm về xử lý form (controlled components), cấu trúc và chức năng của các thành phần trong React Router DOM (BrowserRouter, Routes, Route, Link).
+- Dành thời gian tìm hiểu sâu hơn về quy trình render của Next.js, đặc biệt là cơ chế server-side rendering (SSR/SSG) và client-side rendering (hydration).
+- Thực hành viết các đoạn mã mẫu và sau đó tự mình giải thích lại cách hoạt động của chúng để củng cố khả năng diễn đạt kiến thức.</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>2026-02-08T20:51:25.849853</t>
+  </si>
+  <si>
+    <t>2026-02-08T20:51:39.875161</t>
+  </si>
+  <si>
+    <t>[{"questionId":1059,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1060,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"xczc","sampleAnswer":"Trong Next.js, cơ chế server-side liên quan đến việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1061,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1062,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1063,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"zczxc","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Các thành phần chính của Redux bao gồm store (nơi lưu trữ trạng thái), actions (các đối tượng mô tả sự kiện đã xảy ra), và reducers (các hàm thuần túy xác định cách trạng thái thay đổi để phản ứng với actions). Ngoài ra, tài liệu còn nhắc đến thư viện Redux Toolkit giúp đơn giản hóa việc sử dụng Redux.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1064,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1065,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1066,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"xzcxzc","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm định tuyến cơ bản (router basic), khả năng lấy tham số từ URL (router lấy tham số trên url), và chức năng chuyển hướng (chuyển hướng).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1067,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1068,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+Điểm mạnh:
+- Bạn đã trả lời đúng 7/10 câu hỏi trắc nghiệm, cho thấy bạn nắm vững các kiến thức cơ bản liên quan đến API client, memo, thư viện định tuyến, xử lý form bằng state, ref, context và Redux Toolkit.
+- Sự chính xác trong các câu hỏi lựa chọn giúp bạn đạt được 70% tổng điểm.
+Điểm yếu:
+- Bạn chưa trả lời được các câu hỏi tự luận (Câu 2, Câu 5, Câu 8) yêu cầu phân biệt và giải thích khái niệm.
+- Các câu trả lời bạn đưa ra cho các câu hỏi tự luận đều không có nội dung, cho thấy bạn còn gặp khó khăn trong việc trình bày hoặc chưa nắm rõ sâu các khái niệm này.
+Gợi ý ôn tập:
+- Tập trung ôn lại các khái niệm trọng tâm của Next.js như cơ chế server-side và client-side, hiểu rõ sự khác biệt và mục đích sử dụng của từng cơ chế.
+- Xem xét kỹ lại định nghĩa Redux, các thành phần chính của nó (store, actions, reducers) và vai trò của Redux Toolkit trong việc đơn giản hóa quá trình sử dụng.
+- Nắm vững các chức năng cơ bản của router được đề cập trong tài liệu, bao gồm định tuyến, lấy tham số từ URL và chuyển hướng.
+- Thực hành viết lại các định nghĩa và giải thích các khái niệm này bằng lời của mình để củng cố kiến thức.</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>2026-02-08T20:46:20.913627</t>
+  </si>
+  <si>
+    <t>2026-02-08T20:46:35.775443</t>
+  </si>
+  <si>
+    <t>[{"questionId":1049,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1050,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"bd","sampleAnswer":"Trong Next.js, cơ chế server-side liên quan đến việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1051,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1052,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1053,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sấc","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Các thành phần chính của Redux bao gồm store (nơi lưu trữ trạng thái), actions (các đối tượng mô tả sự kiện đã xảy ra), và reducers (các hàm thuần túy xác định cách trạng thái thay đổi để phản ứng với actions). Ngoài ra, tài liệu còn nhắc đến thư viện Redux Toolkit giúp đơn giản hóa việc sử dụng Redux.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1054,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1055,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1056,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sadas","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm định tuyến cơ bản (router basic), khả năng lấy tham số từ URL (router lấy tham số trên url), và chức năng chuyển hướng (chuyển hướng).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1057,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1058,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+Điểm mạnh:
+- Bạn đã trả lời đúng 7/10 câu hỏi trắc nghiệm, cho thấy bạn nắm vững một số kiến thức cơ bản và chi tiết trong tài liệu.
+- Các câu hỏi về API client, memo trong React, thư viện định tuyến, cách xử lý form, ref, context và vai trò của Redux Toolkit đều được bạn trả lời chính xác.
+Điểm yếu:
+- Bạn còn gặp khó khăn trong việc trả lời các câu hỏi tự luận, đặc biệt là các câu yêu cầu phân biệt hoặc giải thích khái niệm.
+- Các câu hỏi về cơ chế server-side và client-side trong Next.js, giải thích Redux và các thành phần chính, cũng như các chức năng cơ bản của router đều chưa được bạn trả lời đúng.
+- Điều này cho thấy bạn cần cải thiện khả năng tổng hợp và diễn đạt kiến thức một cách đầy đủ và chính xác.
+Gợi ý ôn tập:
+- Tập trung ôn lại và hiểu sâu các khái niệm quan trọng như cơ chế render của Next.js (server-side và client-side).
+- Xem kỹ lại cấu trúc và hoạt động của Redux, bao gồm store, actions, reducers và vai trò của Redux Toolkit.
+- Nắm rõ các chức năng cơ bản của router được đề cập trong tài liệu, bao gồm định tuyến, lấy tham số URL và chuyển hướng.
+- Thực hành việc giải thích các khái niệm này bằng lời văn của mình, không chỉ dừng lại ở việc nhận biết đáp án đúng.</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>2026-02-08T20:37:01.809902</t>
+  </si>
+  <si>
+    <t>2026-02-08T20:37:31.429016</t>
+  </si>
+  <si>
+    <t>[{"questionId":1039,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1040,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dcds","sampleAnswer":"Trong Next.js, cơ chế server-side liên quan đến việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1041,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1042,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1043,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ádsad","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Các thành phần chính của Redux bao gồm store (nơi lưu trữ trạng thái), actions (các đối tượng mô tả sự kiện đã xảy ra), và reducers (các hàm thuần túy xác định cách trạng thái thay đổi để phản ứng với actions). Ngoài ra, tài liệu còn nhắc đến thư viện Redux Toolkit giúp đơn giản hóa việc sử dụng Redux.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1044,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1045,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1046,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sad","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm định tuyến cơ bản (router basic), khả năng lấy tham số từ URL (router lấy tham số trên url), và chức năng chuyển hướng (chuyển hướng).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1047,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1048,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Chào Hoàng Anh Nguyễn.
+- Điểm tổng: 70/100
+- Tổng quan:
+- Hoàng Anh đạt 70/100, đây là một kết quả khá tốt, cho thấy em có nền tảng kiến thức cơ bản vững chắc.
+- Em đã trả lời đúng hầu hết các câu hỏi trắc nghiệm, chứng tỏ khả năng ghi nhớ và nhận diện kiến thức tốt.
+- Tuy nhiên, phần trả lời câu hỏi tự luận còn yếu, đây là điểm em cần cải thiện.
+- Lỗi sai nổi bật:
+- Em chưa trả lời được các câu hỏi yêu cầu giải thích sâu về cơ chế hoạt động (như server-side/client-side trong Next.js) hoặc định nghĩa các khái niệm phức tạp cùng thành phần chính (như Redux).</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>2026-02-06T13:32:54.870903</t>
+  </si>
+  <si>
+    <t>2026-02-06T13:40:30.099694</t>
+  </si>
+  <si>
+    <t>[{"questionId":1029,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1030,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"g","sampleAnswer":"Để xử lý form bằng state trong React, chúng ta sử dụng các 'controlled components'. Mỗi input trong form sẽ có giá trị được kiểm soát bởi state của component. Khi người dùng nhập liệu, sự kiện `onChange` sẽ được kích hoạt để cập nhật state, từ đó cập nhật lại giá trị của input. Điều này giúp quản lý và truy cập dữ liệu form một cách dễ dàng và nhất quán.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1031,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1032,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1033,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"g","sampleAnswer":"`router dom` cung cấp các thành phần để xây dựng định tuyến client-side. Các khái niệm cơ bản bao gồm `BrowserRouter` để bao bọc ứng dụng và cung cấp ngữ cảnh định tuyến. `Routes` được dùng để định nghĩa tập hợp các tuyến đường, và `Route` để ánh xạ một URL cụ thể với một component sẽ được render. `Link` được sử dụng để điều hướng giữa các trang mà không cần tải lại toàn bộ trang.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1034,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1035,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1036,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"g","sampleAnswer":"Trong Next.js, cơ chế server-side (như SSR hoặc SSG) là khi trang được render trước trên server và gửi HTML đã hoàn chỉnh đến trình duyệt. Điều này giúp cải thiện SEO và thời gian tải ban đầu. Cơ chế client-side là khi trang được render hoặc tương tác sau khi JavaScript đã được tải xuống và thực thi trên trình duyệt, thường là sau quá trình 'hydration' của Next.js, cho phép các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1037,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":1038,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Chào Hoàng Anh Nguyễn.
+- Điểm tổng của bạn là 70/100, cho thấy bạn có nắm vững nhiều kiến thức cơ bản về React và các thư viện liên quan.
+- Bạn đã trả lời chính xác phần lớn các câu hỏi trắc nghiệm và câu hỏi về mục đích sử dụng các hook/cơ chế.
+- Điểm yếu rõ rệt nhất của bạn là ở các câu hỏi yêu cầu giải thích hoặc mô tả chi tiết các cơ chế hoạt động.
+- Bạn cần củng cố kiến thức về cách xử lý form bằng state trong React, đặc biệt là khái niệm controlled components.
+- Các khái niệm cơ bản về định tuyến với `react-router-dom` và sự phân biệt server-side/client-side trong Next.js cũng là những phần bạn chưa nắm vững.
+- Tập trung ôn luyện và thực hành các chủ đề yêu cầu giải thích, mô tả chi tiết về cách thức hoạt động của các khái niệm.
+- Thực hành xây dựng các form đơn giản trong React để hiểu rõ về `controlled components`, `onChange` và quản lý state.</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>huynamyb2003@gmail.com</t>
+  </si>
+  <si>
+    <t>Hành Nguyễn</t>
+  </si>
+  <si>
+    <t>2026-02-06T11:22:17.208027</t>
+  </si>
+  <si>
+    <t>2026-02-06T11:23:15.261287</t>
+  </si>
+  <si>
+    <t>[{"questionId":1009,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":5,"maxScore":5,"feedback":"Đúng"},{"questionId":1010,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sdsfdghgf","sampleAnswer":"\"memo\" giúp tối ưu hiệu suất bằng cách ghi nhớ kết quả render của component, tránh re-render không cần thiết. \"Callback\" (thường là `useCallback`) giúp ghi nhớ các hàm, ngăn chặn việc tạo lại hàm mới trong mỗi lần render, từ đó tránh re-render các component con phụ thuộc vào hàm đó.","score":0,"maxScore":5,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1011,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":5,"maxScore":5,"feedback":"Đúng"},{"questionId":1012,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":5,"maxScore":5,"feedback":"Đúng"},{"questionId":1013,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sfdsgf","sampleAnswer":"Để xử lý form bằng state, mỗi trường input trong form sẽ được liên kết với một phần của state. Khi người dùng nhập liệu, giá trị của input sẽ được cập nhật vào state thông qua các hàm xử lý sự kiện (ví dụ: `onChange`). Khi form được submit, dữ liệu từ state sẽ được sử dụng để gửi đi.","score":0,"maxScore":5,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1014,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":5,"maxScore":5,"feedback":"Đúng"},{"questionId":1015,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":5,"feedback":"Sai"},{"questionId":1016,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":5,"maxScore":5,"feedback":"Đúng"},{"questionId":1017,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dsfgfh","sampleAnswer":"\"router dom\" cung cấp các chức năng cơ bản như định tuyến (router basic) để quản lý các đường dẫn URL trong ứng dụng. Nó cũng cho phép lấy các tham số từ URL để hiển thị nội dung động và hỗ trợ chức năng chuyển hướng người dùng giữa các trang khác nhau một cách linh hoạt.","score":0,"maxScore":5,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1018,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":5,"feedback":"Sai"},{"questionId":1019,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":5,"maxScore":5,"feedback":"Đúng"},{"questionId":1020,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":5,"feedback":"Sai"},{"questionId":1021,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dsadv","sampleAnswer":"Cơ chế server side trong Next.js cho phép render trang web trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện hiệu suất tải trang và SEO. Ngược lại, cơ chế client side là khi trang web được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường liên quan đến các tương tác động và cập nhật giao diện sau khi tải ban đầu.","score":0,"maxScore":5,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1022,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":5,"maxScore":5,"feedback":"Đúng"},{"questionId":1023,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":5,"maxScore":5,"feedback":"Đúng"},{"questionId":1024,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":5,"feedback":"Sai"},{"questionId":1025,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dv","sampleAnswer":"\"axios\" là một thư viện HTTP client bên thứ ba, cung cấp nhiều tính năng tiện lợi như interceptors, tự động chuyển đổi JSON và xử lý lỗi tốt hơn. Ngược lại, \"fetch\" là một API tích hợp sẵn trong trình duyệt, trả về Promise và yêu cầu xử lý JSON thủ công hơn, cũng như kiểm tra lỗi mạng riêng biệt.","score":0,"maxScore":5,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":1026,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":5,"feedback":"Sai"},{"questionId":1027,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":5,"maxScore":5,"feedback":"Đúng"},{"questionId":1028,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"đáv","sampleAnswer":"Redux là một thư viện quản lý trạng thái (state management) có thể dự đoán được cho các ứng dụng JavaScript, giúp quản lý trạng thái ứng dụng một cách tập trung. Redux Toolkit là một bộ công cụ được khuyến nghị để phát triển Redux, giúp đơn giản hóa quá trình viết code Redux bằng cách cung cấp các tiện ích và quy ước chuẩn, giảm bớt boilerplate code.","score":0,"maxScore":5,"feedback":"Chưa đúng ý trọng tâm."}]</t>
+  </si>
+  <si>
+    <t>Chào Hành Nguyễn,
+- Chào Hành Nguyễn.
+- Điểm tổng: 45/100
+- Tổng quan: Bạn đã đạt được một số điểm cơ bản ở các câu hỏi trắc nghiệm, cho thấy đã có đọc qua tài liệu.
+- Tuy nhiên, điểm số tổng thể còn thấp, cho thấy bạn chưa thực sự nắm vững và hiểu sâu các khái niệm được đề cập.
+- Khả năng diễn đạt và giải thích các khái niệm chi tiết còn rất yếu.
+- Lỗi sai nổi bật: Bạn không trả lời hoặc trả lời không phù hợp với yêu cầu ở tất cả các câu hỏi tự luận (câu 2, 5, 9, 13, 17, 20).
+- Bạn còn nhầm lẫn một số khái niệm quan trọng trong các câu hỏi trắc nghiệm (ví dụ: cách xử lý form, chức năng của router dom, vai trò của axios và fetch).
+- Việc chưa thể trình bày chi tiết chứng tỏ bạn chưa hiểu rõ về vai trò, cơ chế hoạt động cũng như sự khác biệt giữa các công cụ/kỹ thuật.</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>2026-02-06T10:47:50.342102</t>
+  </si>
+  <si>
+    <t>2026-02-06T10:58:39.594230</t>
+  </si>
+  <si>
+    <t>[{"questionId":994,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"IoC là nguyên lý đảo ngược quyền kiểm soát, giúp quản lý object và giảm sự phụ thuộc giữa các class","sampleAnswer":"IoC là nguyên lý thiết kế trong đó Spring Framework chịu trách nhiệm tạo, quản lý, liên kết và huỷ object thay cho lập trình viên. Thay vì class tự new dependency, quyền kiểm soát được đảo ngược cho Spring. IoC cần thiết để tránh phụ thuộc chặt giữa các class, giúp dễ thay đổi implementation, dễ test và làm cho code linh hoạt, dễ bảo trì hơn.","score":2,"maxScore":6,"feedback":"Thiếu ý: Inversion of Control, Spring Framework, giảm phụ thuộc, linh hoạt"},{"questionId":995,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":996,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":997,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Giúp quản lý các @Bean","sampleAnswer":"IoC Container là thành phần lõi của Spring, chịu trách nhiệm tạo các Bean. Nó cũng có nhiệm vụ inject dependency vào các Bean khi cần thiết. Ngoài ra, IoC Container còn quản lý toàn bộ vòng đời của các Bean từ khi tạo đến khi hủy.","score":0,"maxScore":6,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":998,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":999,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":1000,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Client gửi request, DispatcherServlet tiếp nhận request, HandleMapping tìm Controller phù hợp, Controller gọi Service để xử lý logic, xong rồi trả về view","sampleAnswer":"Client gửi request cho DispatcherServlet. DispatcherServlet sử dụng HandlerMapping để ánh xạ tới Controller phù hợp. Controller gọi Service, thiết lập Model dữ liệu và trả về tên View. DispatcherServlet dùng ViewResolver để xác định View, sau đó chuyển Model cho View để render và trả HTTP response về Client.","score":2,"maxScore":6,"feedback":"Thiếu ý: Spring MVC, luồng xử lý, ViewResolver, Model"},{"questionId":1001,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":1002,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":1003,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"@PathVariable để lấy biến trên URL\n@RequestParam lấy tham số trên đường dẫn","sampleAnswer":"`@PathVariable` dùng để lấy dữ liệu trực tiếp từ URL, xác định tài nguyên cụ thể, giúp URL rõ ràng và đúng chuẩn RESTful. Ví dụ: `/users/{id}`. Ngược lại, `@RequestParam` dùng để lấy dữ liệu từ query string hoặc form nhỏ, thường dùng để lọc, tìm kiếm hoặc truyền tham số đơn giản. Ví dụ: `/products?category=electronics`.","score":4,"maxScore":6,"feedback":"Thiếu ý: query string, RESTful"},{"questionId":1004,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":1005,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":1006,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"JPA là 1 persistence chuẩn trong java dùng để ánh xạ giữa class và bảng trong database\nHibernate là framework ORM dùng để triển khai JPA","sampleAnswer":"JPA (Java Persistence API) là một chuẩn của Java dùng cho ORM, định nghĩa các quy tắc và tiêu chuẩn về cách ánh xạ object Java với database và thao tác dữ liệu. Nó không phải là một framework. Trong khi đó, Hibernate là một ORM framework cụ thể cho Java, có nhiệm vụ ánh xạ object Java với bảng trong cơ sở dữ liệu và thao tác dữ liệu mà không cần SQL thuần. Hibernate triển khai chuẩn JPA và cũng có thể hoạt động độc lập.","score":6,"maxScore":6,"feedback":"Tốt ✅ Đủ ý chính theo rubric."},{"questionId":1007,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":1008,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hành Nguyễn,
+- Chào Hành Nguyễn.
+- Bạn đã hoàn thành bài kiểm tra với tổng điểm 84/100, đây là một kết quả khá tốt và cho thấy bạn nắm vững nhiều kiến thức cơ bản về Spring Framework và Spring MVC.
+- Bạn đặc biệt xuất sắc ở các câu hỏi trắc nghiệm và câu hỏi định nghĩa trực tiếp, thể hiện khả năng ghi nhớ và nhận diện khái niệm tốt.
+- Các câu hỏi yêu cầu giải thích sâu về cơ chế hoạt động (như Inversion of Control, luồng xử lý Spring MVC) hoặc liệt kê trách nhiệm của các thành phần (IoC Container) còn thiếu nhiều chi tiết quan trọng.
+- Câu trả lời về Inversion of Control và IoC Container còn quá ngắn gọn, chưa làm nổi bật được đầy đủ vai trò và lợi ích cốt lõi.
+- Mô tả luồng xử lý HTTP request trong Spring MVC chưa đầy đủ các bước và thành phần quan trọng như `ViewResolver`, `Model` và quá trình `render` view.
+- Bạn cần trình bày rõ ràng và chi tiết hơn khi phân biệt các khái niệm tương tự như `@PathVariable` và `@RequestParam` để làm nổi bật sự khác biệt về mục đích và cách lấy dữ liệu.
+- Hãy dành thời gian đọc kỹ và hiểu sâu hơn về cơ chế hoạt động của IoC và IoC Container, đặc biệt là các trách nhiệm chính như tạo, quản lý vòng đời và inject dependency cho Bean.</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>2026-02-06T10:31:53.884590</t>
+  </si>
+  <si>
+    <t>2026-02-06T10:41:51.796101</t>
+  </si>
+  <si>
+    <t>[{"questionId":979,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ioc là nguyên lý đảo ngược điều khiển giúp tạo và quản lý vòng đời của bean cho spring quản lý thay vì lập trình viên giúp tạo dự án nhanh giảm cấu hình thủ công","sampleAnswer":"IoC là nguyên lý thiết kế trong đó Spring Framework chịu trách nhiệm tạo, quản lý, liên kết và huỷ object thay cho lập trình viên. Thay vì class tự new dependency, quyền kiểm soát được đảo ngược cho Spring. IoC cần thiết để tránh phụ thuộc chặt giữa các class, giúp dễ thay đổi implementation, dễ test và làm cho code linh hoạt, dễ bảo trì hơn.","score":0,"maxScore":6,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":980,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":7,"feedback":"Sai"},{"questionId":981,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":982,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"lưu trữ và quản lý bean","sampleAnswer":"IoC Container là thành phần lõi của Spring, chịu trách nhiệm tạo các Bean. Nó cũng có nhiệm vụ inject dependency vào các Bean khi cần thiết. Ngoài ra, IoC Container còn quản lý toàn bộ vòng đời của các Bean từ khi tạo đến khi hủy.","score":0,"maxScore":6,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":983,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":984,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":985,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"request - dispatcher serverlet -controller - view resolver - view - response","sampleAnswer":"Client gửi request cho DispatcherServlet. DispatcherServlet sử dụng HandlerMapping để ánh xạ tới Controller phù hợp. Controller gọi Service, thiết lập Model dữ liệu và trả về tên View. DispatcherServlet dùng ViewResolver để xác định View, sau đó chuyển Model cho View để render và trả HTTP response về Client.","score":0,"maxScore":6,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":986,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":987,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":988,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"@PathVariable là lấy dữ liệu thông qua url\\\n@RequestMapping là map dữ liệu trên thanh url","sampleAnswer":"`@PathVariable` dùng để lấy dữ liệu trực tiếp từ URL, xác định tài nguyên cụ thể, giúp URL rõ ràng và đúng chuẩn RESTful. Ví dụ: `/users/{id}`. Ngược lại, `@RequestParam` dùng để lấy dữ liệu từ query string hoặc form nhỏ, thường dùng để lọc, tìm kiếm hoặc truyền tham số đơn giản. Ví dụ: `/products?category=electronics`.","score":2,"maxScore":6,"feedback":"Thiếu ý: @RequestParam, query string, RESTful, tham số"},{"questionId":989,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":990,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"},{"questionId":991,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Jpa là 1 java persistence là chuẩn để map dữ liệu từ class đến table trong database\nHibernate là famwork ORM để triển khai jpa","sampleAnswer":"JPA (Java Persistence API) là một chuẩn của Java dùng cho ORM, định nghĩa các quy tắc và tiêu chuẩn về cách ánh xạ object Java với database và thao tác dữ liệu. Nó không phải là một framework. Trong khi đó, Hibernate là một ORM framework cụ thể cho Java, có nhiệm vụ ánh xạ object Java với bảng trong cơ sở dữ liệu và thao tác dữ liệu mà không cần SQL thuần. Hibernate triển khai chuẩn JPA và cũng có thể hoạt động độc lập.","score":5,"maxScore":6,"feedback":"Thiếu ý: framework"},{"questionId":992,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":7,"feedback":"Sai"},{"questionId":993,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":7,"maxScore":7,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hành Nguyễn,
+- Bạn làm xong bài, hãy xem lại các câu sai để rút kinh nghiệm.
+- Ưu tiên ôn lại phần kiến thức nền và ví dụ trong học liệu.
+- Làm lại bài với thời gian giới hạn để tăng tốc độ.</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>hoanganhyb2003@gmail.com</t>
+  </si>
+  <si>
+    <t>Hoang Anh Nguyen</t>
+  </si>
+  <si>
+    <t>2026-02-06T08:55:26.345339</t>
+  </si>
+  <si>
+    <t>2026-02-06T08:56:41.159522</t>
+  </si>
+  <si>
+    <t>[{"questionId":969,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":970,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dfsfgh","sampleAnswer":"Để xử lý form bằng state trong React, chúng ta sử dụng các 'controlled components'. Mỗi input trong form sẽ có giá trị được kiểm soát bởi state của component. Khi người dùng nhập liệu, sự kiện `onChange` sẽ được kích hoạt để cập nhật state, từ đó cập nhật lại giá trị của input. Điều này giúp quản lý và truy cập dữ liệu form một cách dễ dàng và nhất quán.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":971,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":972,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":973,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dsafdsgfd","sampleAnswer":"`router dom` cung cấp các thành phần để xây dựng định tuyến client-side. Các khái niệm cơ bản bao gồm `BrowserRouter` để bao bọc ứng dụng và cung cấp ngữ cảnh định tuyến. `Routes` được dùng để định nghĩa tập hợp các tuyến đường, và `Route` để ánh xạ một URL cụ thể với một component sẽ được render. `Link` được sử dụng để điều hướng giữa các trang mà không cần tải lại toàn bộ trang.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":974,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":975,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":976,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dfsdf","sampleAnswer":"Trong Next.js, cơ chế server-side (như SSR hoặc SSG) là khi trang được render trước trên server và gửi HTML đã hoàn chỉnh đến trình duyệt. Điều này giúp cải thiện SEO và thời gian tải ban đầu. Cơ chế client-side là khi trang được render hoặc tương tác sau khi JavaScript đã được tải xuống và thực thi trên trình duyệt, thường là sau quá trình 'hydration' của Next.js, cho phép các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":977,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":978,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoang Anh Nguyen,
+- Bạn làm xong bài, hãy xem lại các câu sai để rút kinh nghiệm.
+- Ưu tiên ôn lại phần kiến thức nền và ví dụ trong học liệu.
+- Làm lại bài với thời gian giới hạn để tăng tốc độ.</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>2026-02-05T17:26:37.654835</t>
+  </si>
+  <si>
+    <t>2026-02-05T17:28:13.014434</t>
+  </si>
+  <si>
+    <t>[{"questionId":959,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"wfgfdhf","sampleAnswer":"Trong Next.js, cơ chế server-side là việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động và cập nhật nội dung sau khi trang đã tải.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":960,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":961,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":962,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"gfhk","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm: định tuyến cơ bản (router basic) để xác định các đường dẫn và hiển thị nội dung tương ứng; khả năng lấy tham số từ URL (router lấy tham số trên url) cho phép trích xuất dữ liệu động từ đường dẫn; và chức năng chuyển hướng (chuyển hướng) để điều hướng người dùng từ một trang này sang trang khác.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":963,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":964,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":965,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":966,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"gfhjh","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Store là nơi lưu trữ trạng thái toàn bộ ứng dụng. Actions là các đối tượng mô tả sự kiện đã xảy ra, báo hiệu cho Redux biết có điều gì đó cần thay đổi. Reducers là các hàm thuần túy nhận vào trạng thái hiện tại và một action, sau đó trả về trạng thái mới dựa trên action đó.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":967,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":968,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Chào Hoàng Anh Nguyễn,
+- Điểm tổng 40/100 cho thấy bạn cần cải thiện đáng kể về kiến thức cơ bản trong cả Next.js và Redux.
+- Bạn đã nắm được một số khái niệm cơ bản về Redux và Router qua các câu hỏi trắc nghiệm, nhưng còn nhiều lỗ hổng cần lấp đầy.
+- Khả năng diễn giải và trình bày kiến thức cho các câu hỏi mở còn rất yếu hoặc chưa được thực hiện.
+- Toàn bộ các câu hỏi tự luận (câu 1, 4, 8) đều không đạt điểm, bạn cần đưa ra câu trả lời có nội dung liên quan thay vì các ký tự ngẫu nhiên.
+- Bạn còn nhầm lẫn đáng kể về cơ chế render server-side và client-side trong Next.js (câu 3, 7).
+- Kiến thức về vai trò của các thành phần trong Redux, đặc biệt là `reducers`, cần được củng cố (câu 10).
+- Dù đã trả lời đúng một số câu trắc nghiệm, việc thiếu sót ở các câu tự luận cho thấy bạn chưa thực sự hiểu sâu và có thể diễn đạt các khái niệm.</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>2026-02-05T17:24:24.478468</t>
+  </si>
+  <si>
+    <t>2026-02-05T17:25:14.804054</t>
+  </si>
+  <si>
+    <t>[{"questionId":949,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":950,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ádfg","sampleAnswer":"Trong Next.js, cơ chế server-side liên quan đến việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":951,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":952,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":953,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"fsdgfhg","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Các thành phần chính của Redux bao gồm store (nơi lưu trữ trạng thái), actions (các đối tượng mô tả sự kiện đã xảy ra), và reducers (các hàm thuần túy xác định cách trạng thái thay đổi để phản ứng với actions). Ngoài ra, tài liệu còn nhắc đến thư viện Redux Toolkit giúp đơn giản hóa việc sử dụng Redux.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":954,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":955,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":956,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dfsf","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm định tuyến cơ bản (router basic), khả năng lấy tham số từ URL (router lấy tham số trên url), và chức năng chuyển hướng (chuyển hướng).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":957,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":958,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Chào Hoàng Anh Nguyễn.
+- Tổng điểm của bạn là 70/100, cho thấy bạn đã nắm vững các kiến thức cơ bản về định nghĩa và mục đích sử dụng của nhiều khái niệm trong tài liệu.
+- Bạn đã trả lời đúng hầu hết các câu hỏi trắc nghiệm/ngắn, thể hiện khả năng nhận diện các khái niệm chính khá tốt.
+- Tuy nhiên, bạn còn gặp khó khăn với các câu hỏi yêu cầu giải thích sâu hoặc phân biệt chi tiết các khái niệm.
+- Lỗi sai nổi bật:
+- Bạn chưa đưa ra câu trả lời phù hợp cho các câu hỏi tự luận (câu 2, 5, 8), chỉ điền các ký tự không liên quan.
+- Bạn chưa phân biệt được cơ chế server-side và client-side trong Next.js theo tài liệu.
+- Bạn chưa giải thích được Redux và các thành phần chính của nó.</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>2026-02-05T17:16:27.759730</t>
+  </si>
+  <si>
+    <t>2026-02-05T17:22:12.202481</t>
+  </si>
+  <si>
+    <t>[{"questionId":939,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":940,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"dfdgfdgf","sampleAnswer":"useState dùng để quản lý state cục bộ trong một component, khiến component render lại khi state thay đổi. Ngược lại, useContext dùng để chia sẻ state chung cho nhiều component mà không cần truyền props qua nhiều tầng, tránh props drilling.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":941,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":942,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":943,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ấdfh.","sampleAnswer":"Redux Toolkit giúp viết Redux ngắn gọn, dễ hiểu và chuẩn hơn. Nó giảm đáng kể lượng code cần viết so với Redux truyền thống, vốn yêu cầu nhiều file, action, type và reducer. RTK cũng dễ học, dễ dùng và tự động tối ưu hiệu năng.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":944,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":945,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":946,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"rtyk","sampleAnswer":"React Router DOM cho phép tạo nhiều trang trong ứng dụng React mà không cần reload trình duyệt, xây dựng ứng dụng SPA. Nó định nghĩa ánh xạ giữa URL và Component, giúp render Component tương ứng khi người dùng truy cập một URL. Ngoài ra, nó còn hỗ trợ lấy tham số từ URL và chuyển hướng trang.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":947,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":948,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Chào Hoàng Anh Nguyễn.
+- Điểm tổng: 30/100
+- Điểm số 30/100 cho thấy bạn cần củng cố lại kiến thức nền tảng về React và các thư viện liên quan.
+- Bạn chỉ trả lời đúng các câu trắc nghiệm về một số hook cơ bản.
+- Hầu hết các câu hỏi về kiến thức chuyên sâu hoặc giải thích đều chưa được trả lời hoặc trả lời chưa đúng.
+- Thiếu kiến thức cơ bản về nhiều React Hooks quan trọng như `useState` (mục đích sâu hơn), `useContext`, `useEffect` và `useRef`.
+- Chưa nắm vững cách thức quản lý state toàn cục với Redux Toolkit và định tuyến với React Router DOM.
+- Khó khăn trong việc so sánh và nhận diện ưu điểm của các thư viện phổ biến (Next.js, Axios).</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>lich@gmail.com</t>
+  </si>
+  <si>
+    <t>Lịch</t>
+  </si>
+  <si>
+    <t>2026-02-05T16:57:01.892416</t>
+  </si>
+  <si>
+    <t>2026-02-05T17:03:14.611208</t>
+  </si>
+  <si>
+    <t>[{"questionId":929,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":930,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Giúp ánh xạ các yêu cầu(request) đến URL\nCó nhiệm vụ xử lý các yêu cầu từ người dùng\nKhai báo các tham số của yêu cầu\nCó thể xử lý các trường hợp ngoại lệ\n@Controller","sampleAnswer":"Controller trong Spring MVC có ý nghĩa là xử lý các request từ người dùng và trả về phản hồi. Spring MVC cung cấp các annotation như @Controller và @RestController để khai báo các controller. Các annotation này thực hiện các nhiệm vụ như ánh xạ tới URL, khai báo tham số của request và xử lý ngoại lệ.","score":2,"maxScore":10,"feedback":"Thiếu ý: Controller ý nghĩa, Controller annotation, @RestController, xử lý request"},{"questionId":931,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":932,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":933,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"@ComponentScan","sampleAnswer":"Để tự động phát hiện controller, cần khai báo thuộc tính component-scan cho ứng dụng. Với cấu hình Java, sử dụng annotation @ComponentScan trên một lớp cấu hình, ví dụ @ComponentScan(\"com.codegym.web\"). Với cấu hình XML, thêm thẻ &lt;context:component-scan base-package=\"com.codegym.web\"/&gt; vào file cấu hình XML của Spring.","score":2,"maxScore":10,"feedback":"Thiếu ý: tự động phát hiện controller, component-scan, cấu hình Java, cấu hình XML"},{"questionId":934,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":935,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":936,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"@GetMapping là xem\n@PostMapping là thêm sửa xóa","sampleAnswer":"@RequestMapping có thể ánh xạ request dựa trên nhiều thuộc tính. Ví dụ, thuộc tính URL để ánh xạ theo đường dẫn của request. Thuộc tính HTTP Method để ánh xạ theo phương thức HTTP (GET, POST, v.v.). Thuộc tính params được dùng để ánh xạ tới các tham số cụ thể của request.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":937,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":938,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Lịch,
+- Chào Lịch.
+- Điểm tổng: 74/100
+- Lịch có kết quả tổng quan khá tốt với 74/100 điểm, cho thấy bạn đã nắm được nhiều kiến thức nền tảng.
+- Bạn hoàn thành xuất sắc các câu hỏi trắc nghiệm, đạt điểm tuyệt đối ở phần này.
+- Tuy nhiên, điểm yếu rõ rệt nằm ở các câu hỏi tự luận yêu cầu giải thích và trình bày chi tiết.
+- Câu trả lời tự luận của Lịch thường quá ngắn gọn hoặc chưa đầy đủ ý theo yêu cầu của đề bài.
+- Bạn nhầm lẫn giữa các annotation tiện ích (@GetMapping, @PostMapping) với các thuộc tính cấu hình của @RequestMapping.
+- Kiến thức về cấu hình XML để tự động phát hiện controller còn thiếu sót khi được hỏi chi tiết.</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>2026-02-05T16:47:03.513561</t>
+  </si>
+  <si>
+    <t>2026-02-05T16:55:33.819044</t>
+  </si>
+  <si>
+    <t>[{"questionId":919,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":920,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"@Controller, @Component","sampleAnswer":"Controller trong Spring MVC có ý nghĩa là xử lý các request từ người dùng và trả về phản hồi. Spring MVC cung cấp các annotation như @Controller và @RestController để khai báo các controller. Các annotation này thực hiện các nhiệm vụ như ánh xạ tới URL, khai báo tham số của request và xử lý ngoại lệ.","score":2,"maxScore":10,"feedback":"Thiếu ý: Controller ý nghĩa, Controller annotation, @RestController, xử lý request"},{"questionId":921,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":922,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":923,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Quên rồi","sampleAnswer":"Để tự động phát hiện controller, cần khai báo thuộc tính component-scan cho ứng dụng. Với cấu hình Java, sử dụng annotation @ComponentScan trên một lớp cấu hình, ví dụ @ComponentScan(\"com.codegym.web\"). Với cấu hình XML, thêm thẻ &lt;context:component-scan base-package=\"com.codegym.web\"/&gt; vào file cấu hình XML của Spring.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":924,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":925,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":926,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"@PostMapping\n@GetMapping\n@RequestMapping","sampleAnswer":"@RequestMapping có thể ánh xạ request dựa trên nhiều thuộc tính. Ví dụ, thuộc tính URL để ánh xạ theo đường dẫn của request. Thuộc tính HTTP Method để ánh xạ theo phương thức HTTP (GET, POST, v.v.). Thuộc tính params được dùng để ánh xạ tới các tham số cụ thể của request, và headers để ánh xạ dựa trên các header của request.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":927,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":928,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"}]</t>
+  </si>
+  <si>
+    <t>Chào Lịch,
+- Chào Lịch.
+- Điểm tổng: 52/100
+- Chào Lịch. Bạn đã đạt 52/100 điểm cho bài kiểm tra này.
+- Bạn đã nắm được một số kiến thức cơ bản về khai báo controller và một số annotation thông dụng.
+- Tuy nhiên, nhiều câu hỏi yêu cầu giải thích chi tiết hoặc có độ phức tạp cao hơn thì bạn còn gặp khó khăn.
+- Lỗi sai nổi bật:
+- Bạn chưa hiểu rõ ý nghĩa, các thuộc tính chi tiết của `@RequestMapping` và cách sử dụng chúng để ánh xạ request (ví dụ câu 8, câu 10).
+- Kiến thức về cách cấu hình tự động phát hiện controller còn yếu, đặc biệt là với cấu hình XML (câu 5).</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>2026-02-05T16:37:42.756805</t>
+  </si>
+  <si>
+    <t>2026-02-05T16:43:25.986019</t>
+  </si>
+  <si>
+    <t>[{"questionId":909,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":910,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Giảm phụ thuộc code\nDễ test","sampleAnswer":"IoC Container là thành phần lõi của Spring, chịu trách nhiệm tạo bean, inject dependency và quản lý vòng đời bean. ApplicationContext là một loại IoC Container nâng cao, được dùng phổ biến và mặc định trong Spring Boot, cung cấp nhiều tính năng hơn BeanFactory.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":911,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":912,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":913,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Đảo ngược quyền điều khiển cho Spring, giảm phụ thuộc vào tạo mới","sampleAnswer":"Mục đích chính của IoC là đảo ngược quyền kiểm soát việc tạo dependency cho Spring Framework, thay vì class tự tạo. Điều này giúp code dễ test hơn vì các dependency có thể được mock hoặc thay thế dễ dàng trong quá trình kiểm thử, giảm sự phụ thuộc chặt giữa các class.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":914,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":915,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"A","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":916,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Vai trò của Client là gửi request\nVai trò của DispatcherServlet là nhận request\nVai trò của HandlerMapping là tìm Controller phù hợp","sampleAnswer":"Client là nơi gửi HTTP request ban đầu. DispatcherServlet là Servlet trung tâm nhận mọi request và điều phối chúng. HandlerMapping được DispatcherServlet sử dụng để ánh xạ request đến Controller phù hợp dựa trên URL.","score":8,"maxScore":10,"feedback":"Thiếu ý: HTTP request"},{"questionId":917,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":918,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Lịch,
+- Chào Lịch.
+- Điểm tổng: 78/100
+- Lịch có kiến thức nền tảng tốt về Spring và Spring MVC, thể hiện qua việc làm đúng hầu hết các câu hỏi trắc nghiệm.
+- Tuy nhiên, cần cải thiện khả năng giải thích chi tiết các khái niệm và vai trò của từng thành phần trong hệ thống.
+- Điểm 78/100 là một kết quả tốt, cho thấy sự nỗ lực và hiểu bài.
+- Chưa nắm rõ các trách nhiệm chính của IoC Container (như tạo bean, inject dependency, quản lý vòng đời) và vai trò cụ thể của ApplicationContext.
+- Giải thích mục đích của IoC còn chung chung, chưa làm rõ mối liên hệ trực tiếp với việc giúp code dễ test hơn.
+- Mô tả vai trò của DispatcherServlet còn đơn giản, chưa làm nổi bật chức năng điều phối request trung tâm.</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>2026-02-05T16:24:06.100203</t>
+  </si>
+  <si>
+    <t>2026-02-05T16:36:12.426067</t>
+  </si>
+  <si>
+    <t>[{"questionId":899,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":900,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Spring quản lý","sampleAnswer":"IoC Container là thành phần lõi của Spring, chịu trách nhiệm tạo bean, inject dependency và quản lý vòng đời bean. Nó đảm bảo các object được khởi tạo và liên kết đúng cách. Hai loại IoC Container phổ biến là BeanFactory (cơ bản, nhẹ) và ApplicationContext (nâng cao, dùng phổ biến, mặc định trong Spring Boot).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":901,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":902,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":903,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"trong spring mvc mọi request được dispatcherservlet tiếp nhận đóng vai trò là  front controller điều phối luồng xử lý\ndispatcherserlet sử dụng handler mapping để xác định controller, và phương thức xử lý request phù hợp sau đó sử dụng handalrapter để gọi controller.\ncontroller xử lý nghiệm vụ, chuẩn bị dữ liệu trong model, và trả về tên view\ndispatchersevlet gọi viewresolver xác định view tương ứng, render dữ liệu trong model phản hồi lại cho người dùng","sampleAnswer":"Client gửi request cho DispatcherServlet. DispatcherServlet sử dụng HandlerMapping để ánh xạ tới Controller phù hợp. Controller gọi các phương thức xử lý, thiết lập Model dữ liệu và trả về tên View. DispatcherServlet dùng ViewResolver để xác định View, sau đó chuyển Model cho View để render và trả HTTP response về cho Client.","score":5,"maxScore":10,"feedback":"Thiếu ý: Client, HandlerMapping, Response"},{"questionId":904,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":905,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":906,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"giúp lập trình viên không phải tự tạo mới, Spring làm hết","sampleAnswer":"IoC là nguyên lý thiết kế trong đó Spring Framework chịu trách nhiệm tạo, quản lý, liên kết và huỷ object thay cho lập trình viên. Mục đích chính là đảo ngược quyền kiểm soát việc tạo dependency cho Spring. Các lợi ích bao gồm tránh phụ thuộc chặt giữa các class, dễ thay đổi implementation, dễ test (mock), và giúp code linh hoạt, dễ bảo trì.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":907,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":908,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Lịch,
+- Chào Lịch.
+- Điểm tổng: 65/100
+- Điểm tổng 65/100 cho thấy bạn có nắm được kiến thức cơ bản về Spring MVC và IoC.
+- Bạn làm tốt các câu hỏi dạng trắc nghiệm, thể hiện việc ghi nhớ định nghĩa và nguyên lý trực tiếp.
+- Tuy nhiên, khả năng giải thích chi tiết và đầy đủ các khái niệm còn hạn chế.
+- Thiếu kiến thức sâu về mục đích, lợi ích của Inversion of Control và trách nhiệm của IoC Container.
+- Sai kiến thức cơ bản về annotation dùng để đánh dấu Spring Bean.
+- Mô tả luồng xử lý HTTP request trong Spring MVC còn thiếu một số chi tiết quan trọng.</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>2026-02-05T15:01:36.305096</t>
+  </si>
+  <si>
+    <t>2026-02-05T15:02:41.158259</t>
+  </si>
+  <si>
+    <t>[{"questionId":889,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":890,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sdf","sampleAnswer":"Để xử lý form bằng state trong React, chúng ta sử dụng các 'controlled components'. Mỗi input trong form sẽ có giá trị được kiểm soát bởi state của component. Khi người dùng nhập liệu, sự kiện `onChange` sẽ được kích hoạt để cập nhật state, từ đó cập nhật lại giá trị của input. Điều này giúp quản lý và truy cập dữ liệu form một cách dễ dàng và nhất quán.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":891,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":892,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":893,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sadsa","sampleAnswer":"`router dom` cung cấp các thành phần để xây dựng định tuyến client-side. Các khái niệm cơ bản bao gồm `BrowserRouter` để bao bọc ứng dụng và cung cấp ngữ cảnh định tuyến. `Routes` được dùng để định nghĩa tập hợp các tuyến đường, và `Route` để ánh xạ một URL cụ thể với một component sẽ được render. `Link` được sử dụng để điều hướng giữa các trang mà không cần tải lại toàn bộ trang.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":894,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":895,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":896,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sà","sampleAnswer":"Trong Next.js, cơ chế server-side (như SSR hoặc SSG) là khi trang được render trước trên server và gửi HTML đã hoàn chỉnh đến trình duyệt. Điều này giúp cải thiện SEO và thời gian tải ban đầu. Cơ chế client-side là khi trang được render hoặc tương tác sau khi JavaScript đã được tải xuống và thực thi trên trình duyệt, thường là sau quá trình 'hydration' của Next.js, cho phép các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":897,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":898,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Chào Hoàng Anh Nguyễn.
+- Hoàng Anh đã thể hiện sự nắm vững các khái niệm cơ bản về React và Next.js qua các câu hỏi trắc nghiệm.
+- Điểm số 70/100 cho thấy bạn đã đạt được mức độ hiểu biết khá tốt về các chủ đề cốt lõi.
+- Tuy nhiên, khả năng diễn đạt và giải thích sâu các khái niệm còn là điểm cần cải thiện.
+- Bạn chưa nắm vững hoàn toàn về cơ chế xử lý form bằng state (controlled components) trong React.
+- Các khái niệm cơ bản về `react-router-dom` cần được ôn tập chi tiết hơn.
+- Bạn còn gặp khó khăn trong việc phân biệt cơ chế server-side và client-side rendering của Next.js.
+- Khả năng giải thích và trình bày các vấn đề dưới dạng tự luận còn rất hạn chế.</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>2026-02-05T12:06:02.129621</t>
+  </si>
+  <si>
+    <t>2026-02-05T12:07:01.850844</t>
+  </si>
+  <si>
+    <t>[{"questionId":879,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":880,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"\\xc","sampleAnswer":"Trong Next.js, cơ chế server-side liên quan đến việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":881,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":882,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":883,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sad","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Các thành phần chính của Redux bao gồm store (nơi lưu trữ trạng thái), actions (các đối tượng mô tả sự kiện đã xảy ra), và reducers (các hàm thuần túy xác định cách trạng thái thay đổi để phản ứng với actions). Ngoài ra, tài liệu còn nhắc đến thư viện Redux Toolkit giúp đơn giản hóa việc sử dụng Redux.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":884,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":885,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":886,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sd","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm định tuyến cơ bản (router basic), khả năng lấy tham số từ URL (router lấy tham số trên url), và chức năng chuyển hướng (chuyển hướng).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":887,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":888,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Bạn làm xong bài, hãy xem lại các câu sai để rút kinh nghiệm.
+- Ưu tiên ôn lại phần kiến thức nền và ví dụ trong học liệu.
+- Làm lại bài với thời gian giới hạn để tăng tốc độ.</t>
+  </si>
+  <si>
+    <t>2026-02-05T11:53:55.743397</t>
+  </si>
+  <si>
+    <t>2026-02-05T11:55:18.865392</t>
+  </si>
+  <si>
+    <t>[{"questionId":869,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":870,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ádasd","sampleAnswer":"Để xử lý form bằng state trong React, chúng ta sử dụng các 'controlled components'. Mỗi input trong form sẽ có giá trị được kiểm soát bởi state của component. Khi người dùng nhập liệu, sự kiện `onChange` sẽ được kích hoạt để cập nhật state, từ đó cập nhật lại giá trị của input. Điều này giúp quản lý và truy cập dữ liệu form một cách dễ dàng và nhất quán.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":871,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":872,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":873,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sadsa","sampleAnswer":"`router dom` cung cấp các thành phần để xây dựng định tuyến client-side. Các khái niệm cơ bản bao gồm `BrowserRouter` để bao bọc ứng dụng và cung cấp ngữ cảnh định tuyến. `Routes` được dùng để định nghĩa tập hợp các tuyến đường, và `Route` để ánh xạ một URL cụ thể với một component sẽ được render. `Link` được sử dụng để điều hướng giữa các trang mà không cần tải lại toàn bộ trang.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":874,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":875,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":876,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sadsad","sampleAnswer":"Trong Next.js, cơ chế server-side (như SSR hoặc SSG) là khi trang được render trước trên server và gửi HTML đã hoàn chỉnh đến trình duyệt. Điều này giúp cải thiện SEO và thời gian tải ban đầu. Cơ chế client-side là khi trang được render hoặc tương tác sau khi JavaScript đã được tải xuống và thực thi trên trình duyệt, thường là sau quá trình 'hydration' của Next.js, cho phép các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":877,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":878,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Hoàng Anh Nguyễn,
+- Chào Hoàng Anh Nguyễn,
+- Điểm tổng 70/100 cho thấy bạn có kiến thức nền tảng tốt về các khái niệm cơ bản trong React và Next.js.
+- Bạn đã trả lời đúng tất cả các câu hỏi trắc nghiệm, thể hiện sự nắm vững các định nghĩa và cách sử dụng cơ bản của các tính năng.
+- Tuy nhiên, kỹ năng trình bày và giải thích các khái niệm chi tiết qua các câu hỏi tự luận còn cần được cải thiện.
+- Lỗi sai lớn nhất là bạn chưa hoàn thành hoặc chưa đưa ra câu trả lời đầy đủ cho các câu hỏi yêu cầu mô tả hoặc giải thích.
+- Các khái niệm quan trọng như xử lý form bằng state (controlled components), cơ chế hoạt động của `react-router-dom` và phân biệt server-side/client-side rendering trong Next.js cần được hiểu và diễn đạt rõ ràng hơn.
+- Việc thiếu sót trong các câu trả lời tự luận đã ảnh hưởng đáng kể đến điểm số tổng thể.
+- Tập trung ôn luyện cách giải thích và mô tả các khái niệm chuyên sâu, không chỉ dừng lại ở việc nhớ định nghĩa.</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>bao@gmail.com</t>
+  </si>
+  <si>
+    <t>Bảo</t>
+  </si>
+  <si>
+    <t>2026-02-05T09:29:10.174079</t>
+  </si>
+  <si>
+    <t>2026-02-05T09:29:25.471244</t>
+  </si>
+  <si>
+    <t>[{"questionId":859,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":860,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ssad","sampleAnswer":"Trong Next.js, cơ chế server-side liên quan đến việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":861,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":862,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":863,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sads","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Các thành phần chính của Redux bao gồm store (nơi lưu trữ trạng thái), actions (các đối tượng mô tả sự kiện đã xảy ra), và reducers (các hàm thuần túy xác định cách trạng thái thay đổi để phản ứng với actions). Ngoài ra, tài liệu còn nhắc đến thư viện Redux Toolkit giúp đơn giản hóa việc sử dụng Redux.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":864,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":865,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":866,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sad","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm định tuyến cơ bản (router basic), khả năng lấy tham số từ URL (router lấy tham số trên url), và chức năng chuyển hướng (chuyển hướng).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":867,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":868,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Bảo,
+- Chào Bảo.
+- Điểm tổng: 70/100
+- Chúc mừng bạn đã đạt điểm số khá tốt (70/100) trong bài kiểm tra này.
+- Bạn đã nắm vững các kiến thức cơ bản và trả lời chính xác tất cả các câu hỏi trắc nghiệm.
+- Tuy nhiên, kỹ năng trả lời các câu hỏi tự luận/giải thích còn cần cải thiện đáng kể.
+- Bạn chưa trả lời đúng các câu hỏi yêu cầu giải thích về Next.js (cơ chế server-side/client-side), Redux (định nghĩa và thành phần), và các chức năng của router.
+- Các câu trả lời tự luận của bạn rất ngắn gọn và không cung cấp đủ thông tin cần thiết.
+- Điều này cho thấy bạn có thể đã ghi nhớ các khái niệm chính nhưng chưa hiểu sâu hoặc chưa biết cách diễn đạt đầy đủ.</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>quang@gmail.com</t>
+  </si>
+  <si>
+    <t>Quang</t>
+  </si>
+  <si>
+    <t>2026-02-05T09:23:01.726384</t>
+  </si>
+  <si>
+    <t>2026-02-05T09:24:13.425328</t>
+  </si>
+  <si>
+    <t>[{"questionId":849,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":850,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sda","sampleAnswer":"IoC Container là thành phần lõi của Spring, chịu trách nhiệm tạo bean, inject dependency và quản lý vòng đời bean. Nó đảm bảo các object được khởi tạo và liên kết đúng cách. Hai loại IoC Container phổ biến là BeanFactory (cơ bản, nhẹ) và ApplicationContext (nâng cao, dùng phổ biến, mặc định trong Spring Boot).","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":851,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":852,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":853,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"áda","sampleAnswer":"Client gửi request cho DispatcherServlet. DispatcherServlet sử dụng HandlerMapping để ánh xạ tới Controller phù hợp. Controller gọi các phương thức xử lý, thiết lập Model dữ liệu và trả về tên View. DispatcherServlet dùng ViewResolver để xác định View, sau đó chuyển Model cho View để render và trả HTTP response về cho Client.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":854,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":855,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":856,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"ádsa","sampleAnswer":"IoC là nguyên lý thiết kế trong đó Spring Framework chịu trách nhiệm tạo, quản lý, liên kết và huỷ object thay cho lập trình viên. Mục đích chính là đảo ngược quyền kiểm soát việc tạo dependency cho Spring. Các lợi ích bao gồm tránh phụ thuộc chặt giữa các class, dễ thay đổi implementation, dễ test (mock), và giúp code linh hoạt, dễ bảo trì.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":857,"questionType":"MCQ","selectedAnswer":"D","correctAnswer":"D","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":858,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Quang,
+- Chào Quang.
+- Điểm tổng: 60/100
+- Quang đã hoàn thành bài kiểm tra với tổng điểm 60/100, cho thấy bạn có nắm được một số kiến thức cơ bản về Spring.
+- Bạn đã trả lời đúng các câu hỏi trắc nghiệm liên quan đến annotation, phạm vi tồn tại của bean và vai trò của các thành phần trong Spring MVC.
+- Tuy nhiên, phần kiến thức nền tảng và hiểu sâu về các nguyên lý cốt lõi của Spring như IoC, IoC Container và luồng hoạt động của Spring MVC còn nhiều hạn chế.
+- Thiếu sót nghiêm trọng trong việc giải thích và trình bày các khái niệm cơ bản như IoC (Câu 1, Câu 8) và IoC Container (Câu 2). Đây là những kiến thức nền tảng quan trọng nhất của Spring.
+- Không nắm rõ luồng xử lý một HTTP request trong Spring MVC (Câu 5), một kiến thức trọng tâm khi làm việc với các ứng dụng web dùng Spring.
+- Các câu trả lời cho câu hỏi tự luận còn rất sơ sài hoặc không liên quan, cho thấy bạn chưa chuẩn bị kỹ hoặc chưa hiểu bài.</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>2026-02-05T09:13:15.444164</t>
+  </si>
+  <si>
+    <t>2026-02-05T09:18:36.838978</t>
+  </si>
+  <si>
+    <t>[{"questionId":839,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":840,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"trong Next.js, server-side tạo HTML trên máy chủ, tối ưu SEO tốc độ tải đầu, client-side render bằng JavaScript bằng trình duyệt","sampleAnswer":"Trong Next.js, cơ chế server-side liên quan đến việc render trang trên máy chủ trước khi gửi đến trình duyệt, giúp cải thiện SEO và hiệu suất tải trang ban đầu. Ngược lại, cơ chế client-side là khi trang được render hoàn toàn trên trình duyệt của người dùng sau khi tải về, thường được sử dụng cho các tương tác động.","score":10,"maxScore":10,"feedback":"Tốt ✅ Đủ ý chính theo rubric."},{"questionId":841,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":842,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":843,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"Redux là thư viện quản lý trạng thái ứng dụng.\ncác thành phần chính là: store, actions, reducers, Redux Toolkit","sampleAnswer":"Redux là một thư viện quản lý trạng thái ứng dụng. Các thành phần chính của Redux bao gồm store (nơi lưu trữ trạng thái), actions (các đối tượng mô tả sự kiện đã xảy ra), và reducers (các hàm thuần túy xác định cách trạng thái thay đổi để phản ứng với actions). Ngoài ra, tài liệu còn nhắc đến thư viện Redux Toolkit giúp đơn giản hóa việc sử dụng Redux.","score":10,"maxScore":10,"feedback":"Tốt ✅ Đủ ý chính theo rubric."},{"questionId":844,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":845,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":846,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"các chức năng cơ bản của router gồm:\nđịnh tuyến cơ bản (router basic)\nkhả năng lấy tham số từ URL(router lấy tham số trên url)\nchức năng chuyển hướng(chuyển hướng)","sampleAnswer":"Các chức năng cơ bản của router được đề cập bao gồm định tuyến cơ bản (router basic), khả năng lấy tham số từ URL (router lấy tham số trên url), và chức năng chuyển hướng (chuyển hướng).","score":7,"maxScore":10,"feedback":"Thiếu ý: lấy tham số URL"},{"questionId":847,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":848,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
+  </si>
+  <si>
+    <t>Chào Quang,
+- Chào Quang.
+- Điểm tổng: 97/100
+- Em đã hoàn thành bài kiểm tra một cách xuất sắc với số điểm gần như tuyệt đối, thể hiện sự nắm vững kiến thức rất tốt.
+- Em đã trả lời chính xác hầu hết các câu hỏi về định nghĩa, mục đích sử dụng các thư viện và cơ chế trong React, Next.js, và Redux.
+- Khả năng ghi nhớ và áp dụng kiến thức lý thuyết của em rất đáng khen ngợi.
+- Lỗi sai duy nhất là ở câu hỏi về các chức năng cơ bản của router. Mặc dù câu trả lời đã bao gồm các ý chính, có thể một vài chi tiết hoặc cách diễn đạt chưa hoàn toàn đầy đủ như mong đợi.
+- Em hãy xem lại chi tiết phần tài liệu về router để củng cố thêm các khía cạnh nhỏ nhất.
+- Tiếp tục duy trì phong độ học tập này và không ngừng đào sâu hơn vào các khái niệm đã học.</t>
+  </si>
+  <si>
     <t>87</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>hoanganhnd2003@gmail.com</t>
-  </si>
-  <si>
-    <t>Hoàng Anh Nguyễn</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>PRACTICE</t>
   </si>
   <si>
     <t>2026-02-04T16:51:08.886226</t>
@@ -88,9 +774,6 @@
     <t>86</t>
   </si>
   <si>
-    <t>93</t>
-  </si>
-  <si>
     <t>2026-02-04T16:48:23.802722</t>
   </si>
   <si>
@@ -114,9 +797,6 @@
     <t>85</t>
   </si>
   <si>
-    <t>92</t>
-  </si>
-  <si>
     <t>2026-02-04T14:36:12.424293</t>
   </si>
   <si>
@@ -138,15 +818,6 @@
   </si>
   <si>
     <t>84</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>hoanganhyb2003@gmail.com</t>
-  </si>
-  <si>
-    <t>Hoang Anh Nguyen</t>
   </si>
   <si>
     <t>2026-02-04T14:19:22.551509</t>
@@ -172,9 +843,6 @@
     <t>83</t>
   </si>
   <si>
-    <t>90</t>
-  </si>
-  <si>
     <t>2026-02-03T14:07:05.349100</t>
   </si>
   <si>
@@ -198,9 +866,6 @@
     <t>82</t>
   </si>
   <si>
-    <t>89</t>
-  </si>
-  <si>
     <t>2026-02-03T12:37:52.601914</t>
   </si>
   <si>
@@ -222,9 +887,6 @@
   </si>
   <si>
     <t>81</t>
-  </si>
-  <si>
-    <t>88</t>
   </si>
   <si>
     <t>2026-02-03T12:32:53.440453</t>
@@ -602,12 +1264,6 @@
   </si>
   <si>
     <t>[{"questionId":614,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":615,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"asd","sampleAnswer":"Để xử lý form bằng state trong React, chúng ta sử dụng các 'controlled components'. Mỗi input trong form sẽ có giá trị được kiểm soát bởi state của component. Khi người dùng nhập liệu, sự kiện `onChange` sẽ được kích hoạt để cập nhật state, từ đó cập nhật lại giá trị của input. Điều này giúp quản lý và truy cập dữ liệu form một cách dễ dàng và nhất quán.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":616,"questionType":"MCQ","selectedAnswer":"A","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":0,"maxScore":10,"feedback":"Sai"},{"questionId":617,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":618,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"sad","sampleAnswer":"`router dom` cung cấp các thành phần để xây dựng định tuyến client-side. Các khái niệm cơ bản bao gồm `BrowserRouter` để bao bọc ứng dụng và cung cấp ngữ cảnh định tuyến. `Routes` được dùng để định nghĩa tập hợp các tuyến đường, và `Route` để ánh xạ một URL cụ thể với một component sẽ được render. `Link` được sử dụng để điều hướng giữa các trang mà không cần tải lại toàn bộ trang.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":619,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":620,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":621,"questionType":"ESSAY","selectedAnswer":null,"correctAnswer":null,"textAnswer":"đá","sampleAnswer":"Trong Next.js, cơ chế server-side (như SSR hoặc SSG) là khi trang được render trước trên server và gửi HTML đã hoàn chỉnh đến trình duyệt. Điều này giúp cải thiện SEO và thời gian tải ban đầu. Cơ chế client-side là khi trang được render hoặc tương tác sau khi JavaScript đã được tải xuống và thực thi trên trình duyệt, thường là sau quá trình 'hydration' của Next.js, cho phép các tương tác động.","score":0,"maxScore":10,"feedback":"Chưa đúng ý trọng tâm."},{"questionId":622,"questionType":"MCQ","selectedAnswer":"B","correctAnswer":"B","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"},{"questionId":623,"questionType":"MCQ","selectedAnswer":"C","correctAnswer":"C","textAnswer":null,"sampleAnswer":null,"score":10,"maxScore":10,"feedback":"Đúng"}]</t>
-  </si>
-  <si>
-    <t>Chào Hoàng Anh Nguyễn,
-- Bạn làm xong bài, hãy xem lại các câu sai để rút kinh nghiệm.
-- Ưu tiên ôn lại phần kiến thức nền và ví dụ trong học liệu.
-- Làm lại bài với thời gian giới hạn để tăng tốc độ.</t>
   </si>
   <si>
     <t>64</t>
@@ -859,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.18359375" customWidth="true" bestFit="true"/>
@@ -872,7 +1528,7 @@
     <col min="8" max="8" width="24.65234375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.18359375" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="156.35546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="178.55859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -936,7 +1592,7 @@
         <v>18</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="J2" t="s" s="0">
         <v>19</v>
@@ -1006,7 +1662,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>31</v>
@@ -1020,144 +1676,144 @@
         <v>33</v>
       </c>
       <c r="B5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="F5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="H5" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="E5" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s" s="0">
+      <c r="I5" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="J5" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="H5" t="s" s="0">
+      <c r="K5" t="s" s="0">
         <v>38</v>
-      </c>
-      <c r="I5" t="n" s="0">
-        <v>82.0</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="K5" t="s" s="0">
-        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s" s="0">
+      <c r="H6" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="F6" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s" s="0">
+      <c r="I6" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J6" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="H6" t="s" s="0">
+      <c r="K6" t="s" s="0">
         <v>44</v>
-      </c>
-      <c r="I6" t="n" s="0">
-        <v>40.0</v>
-      </c>
-      <c r="J6" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="K6" t="s" s="0">
-        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s" s="0">
+      <c r="H7" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="F7" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s" s="0">
+      <c r="I7" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J7" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="H7" t="s" s="0">
+      <c r="K7" t="s" s="0">
         <v>50</v>
-      </c>
-      <c r="I7" t="n" s="0">
-        <v>24.0</v>
-      </c>
-      <c r="J7" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="K7" t="s" s="0">
-        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s" s="0">
+      <c r="H8" t="s" s="0">
         <v>54</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>56</v>
       </c>
       <c r="I8" t="n" s="0">
         <v>70.0</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>12</v>
@@ -1175,24 +1831,24 @@
         <v>16</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I9" t="n" s="0">
         <v>70.0</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>12</v>
@@ -1210,24 +1866,24 @@
         <v>16</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I10" t="n" s="0">
         <v>70.0</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>12</v>
@@ -1245,33 +1901,33 @@
         <v>16</v>
       </c>
       <c r="G11" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J11" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="H11" t="s" s="0">
+      <c r="K11" t="s" s="0">
         <v>71</v>
-      </c>
-      <c r="I11" t="n" s="0">
-        <v>40.0</v>
-      </c>
-      <c r="J11" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="K11" t="s" s="0">
-        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B12" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>13</v>
-      </c>
       <c r="D12" t="s" s="0">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>33</v>
@@ -1280,129 +1936,129 @@
         <v>16</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>70.0</v>
+        <v>45.0</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>70.0</v>
+        <v>84.0</v>
       </c>
       <c r="J13" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>70.0</v>
+        <v>63.0</v>
       </c>
       <c r="J14" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F15" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>20.0</v>
+        <v>70.0</v>
       </c>
       <c r="J15" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>12</v>
@@ -1414,30 +2070,30 @@
         <v>14</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="J16" t="s" s="0">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>12</v>
@@ -1449,30 +2105,30 @@
         <v>14</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>30.0</v>
+        <v>70.0</v>
       </c>
       <c r="J17" t="s" s="0">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>12</v>
@@ -1484,170 +2140,170 @@
         <v>14</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="J18" t="s" s="0">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I19" t="n" s="0">
-        <v>20.0</v>
+        <v>74.0</v>
       </c>
       <c r="J19" t="s" s="0">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="B20" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>13</v>
-      </c>
       <c r="D20" t="s" s="0">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>30.0</v>
+        <v>52.0</v>
       </c>
       <c r="J20" t="s" s="0">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>60.0</v>
+        <v>78.0</v>
       </c>
       <c r="J21" t="s" s="0">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I22" t="n" s="0">
-        <v>50.0</v>
+        <v>65.0</v>
       </c>
       <c r="J22" t="s" s="0">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>12</v>
@@ -1659,30 +2315,30 @@
         <v>14</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F23" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="I23" t="n" s="0">
-        <v>81.0</v>
+        <v>70.0</v>
       </c>
       <c r="J23" t="s" s="0">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>12</v>
@@ -1694,170 +2350,170 @@
         <v>14</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I24" t="n" s="0">
-        <v>60.0</v>
+        <v>70.0</v>
       </c>
       <c r="J24" t="s" s="0">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F25" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I25" t="n" s="0">
-        <v>77.0</v>
+        <v>70.0</v>
       </c>
       <c r="J25" t="s" s="0">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I26" t="n" s="0">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="J26" t="s" s="0">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="E27" t="s" s="0">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="I27" t="n" s="0">
         <v>60.0</v>
       </c>
       <c r="J27" t="s" s="0">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F28" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="I28" t="n" s="0">
-        <v>30.0</v>
+        <v>97.0</v>
       </c>
       <c r="J28" t="s" s="0">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>12</v>
@@ -1869,30 +2525,30 @@
         <v>14</v>
       </c>
       <c r="E29" t="s" s="0">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F29" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="I29" t="n" s="0">
-        <v>70.0</v>
+        <v>60.0</v>
       </c>
       <c r="J29" t="s" s="0">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>12</v>
@@ -1904,30 +2560,30 @@
         <v>14</v>
       </c>
       <c r="E30" t="s" s="0">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F30" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="I30" t="n" s="0">
-        <v>87.0</v>
+        <v>60.0</v>
       </c>
       <c r="J30" t="s" s="0">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>12</v>
@@ -1939,65 +2595,65 @@
         <v>14</v>
       </c>
       <c r="E31" t="s" s="0">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F31" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I31" t="n" s="0">
-        <v>6.0</v>
+        <v>60.0</v>
       </c>
       <c r="J31" t="s" s="0">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>173</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s" s="0">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="F32" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="I32" t="n" s="0">
-        <v>40.0</v>
+        <v>82.0</v>
       </c>
       <c r="J32" t="s" s="0">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>12</v>
@@ -2009,25 +2665,970 @@
         <v>14</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F33" t="s" s="0">
         <v>16</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="I33" t="n" s="0">
         <v>40.0</v>
       </c>
       <c r="J33" t="s" s="0">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>183</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="I34" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="K34" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="I35" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="K35" t="s" s="0">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="I36" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="K36" t="s" s="0">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="I37" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J37" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="K37" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="H38" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="I38" t="n" s="0">
+        <v>40.0</v>
+      </c>
+      <c r="J38" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="K38" t="s" s="0">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G39" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="H39" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="I39" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J39" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="K39" t="s" s="0">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="F40" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G40" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="H40" t="s" s="0">
+        <v>227</v>
+      </c>
+      <c r="I40" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J40" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="K40" t="s" s="0">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="H41" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="I41" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J41" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="K41" t="s" s="0">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>235</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E42" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="F42" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G42" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="H42" t="s" s="0">
+        <v>237</v>
+      </c>
+      <c r="I42" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="J42" t="s" s="0">
+        <v>238</v>
+      </c>
+      <c r="K42" t="s" s="0">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="F43" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G43" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="H43" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="I43" t="n" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="J43" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="K43" t="s" s="0">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E44" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="F44" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G44" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="H44" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="I44" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="J44" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="K44" t="s" s="0">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="F45" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G45" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="H45" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="I45" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="J45" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="K45" t="s" s="0">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>255</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D46" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E46" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="F46" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G46" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="H46" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="I46" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="J46" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="K46" t="s" s="0">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E47" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="F47" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G47" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="H47" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="I47" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="J47" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="K47" t="s" s="0">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>265</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="E48" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="F48" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G48" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="H48" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="I48" t="n" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="J48" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="K48" t="s" s="0">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>270</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s" s="0">
+        <v>235</v>
+      </c>
+      <c r="F49" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G49" t="s" s="0">
+        <v>271</v>
+      </c>
+      <c r="H49" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="I49" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="J49" t="s" s="0">
+        <v>273</v>
+      </c>
+      <c r="K49" t="s" s="0">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>275</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="F50" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G50" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="H50" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="I50" t="n" s="0">
+        <v>81.0</v>
+      </c>
+      <c r="J50" t="s" s="0">
+        <v>278</v>
+      </c>
+      <c r="K50" t="s" s="0">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="F51" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G51" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="H51" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="I51" t="n" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="J51" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="K51" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="E52" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="F52" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G52" t="s" s="0">
+        <v>285</v>
+      </c>
+      <c r="H52" t="s" s="0">
+        <v>286</v>
+      </c>
+      <c r="I52" t="n" s="0">
+        <v>77.0</v>
+      </c>
+      <c r="J52" t="s" s="0">
+        <v>287</v>
+      </c>
+      <c r="K52" t="s" s="0">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E53" t="s" s="0">
+        <v>255</v>
+      </c>
+      <c r="F53" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G53" t="s" s="0">
+        <v>290</v>
+      </c>
+      <c r="H53" t="s" s="0">
+        <v>291</v>
+      </c>
+      <c r="I53" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="J53" t="s" s="0">
+        <v>292</v>
+      </c>
+      <c r="K53" t="s" s="0">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>294</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E54" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="F54" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G54" t="s" s="0">
+        <v>295</v>
+      </c>
+      <c r="H54" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="I54" t="n" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="J54" t="s" s="0">
+        <v>297</v>
+      </c>
+      <c r="K54" t="s" s="0">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>299</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s" s="0">
+        <v>265</v>
+      </c>
+      <c r="F55" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G55" t="s" s="0">
+        <v>300</v>
+      </c>
+      <c r="H55" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="I55" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="J55" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="K55" t="s" s="0">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>304</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E56" t="s" s="0">
+        <v>270</v>
+      </c>
+      <c r="F56" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G56" t="s" s="0">
+        <v>305</v>
+      </c>
+      <c r="H56" t="s" s="0">
+        <v>306</v>
+      </c>
+      <c r="I56" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="J56" t="s" s="0">
+        <v>307</v>
+      </c>
+      <c r="K56" t="s" s="0">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>309</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E57" t="s" s="0">
+        <v>275</v>
+      </c>
+      <c r="F57" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G57" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="H57" t="s" s="0">
+        <v>311</v>
+      </c>
+      <c r="I57" t="n" s="0">
+        <v>87.0</v>
+      </c>
+      <c r="J57" t="s" s="0">
+        <v>312</v>
+      </c>
+      <c r="K57" t="s" s="0">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>314</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E58" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="F58" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G58" t="s" s="0">
+        <v>315</v>
+      </c>
+      <c r="H58" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="I58" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="J58" t="s" s="0">
+        <v>317</v>
+      </c>
+      <c r="K58" t="s" s="0">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E59" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="F59" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G59" t="s" s="0">
+        <v>320</v>
+      </c>
+      <c r="H59" t="s" s="0">
+        <v>321</v>
+      </c>
+      <c r="I59" t="n" s="0">
+        <v>40.0</v>
+      </c>
+      <c r="J59" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="K59" t="s" s="0">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E60" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="F60" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G60" t="s" s="0">
+        <v>325</v>
+      </c>
+      <c r="H60" t="s" s="0">
+        <v>326</v>
+      </c>
+      <c r="I60" t="n" s="0">
+        <v>40.0</v>
+      </c>
+      <c r="J60" t="s" s="0">
+        <v>327</v>
+      </c>
+      <c r="K60" t="s" s="0">
+        <v>328</v>
       </c>
     </row>
   </sheetData>
